--- a/test-files/graph-tests/dCIN5GendronModel1.xlsx
+++ b/test-files/graph-tests/dCIN5GendronModel1.xlsx
@@ -1,11 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="25823"/>
-  <workbookPr date1904="1" autoCompressPictures="0"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14520" tabRatio="929" activeTab="4"/>
-  </bookViews>
+  <workbookPr codeName="ThisWorkbook" autoCompressPictures="false" date1904="true"/>
   <sheets>
     <sheet name="production_rates" sheetId="1" r:id="rId1"/>
     <sheet name="degradation_rates" sheetId="2" r:id="rId2"/>
@@ -19,293 +15,43 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">dcin5!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="140001" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
-      <mx:ArchID Flags="2"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="79">
-  <si>
-    <t>SystematicName</t>
-  </si>
-  <si>
-    <t>StandardName</t>
-  </si>
-  <si>
-    <t>Production_Rate</t>
-  </si>
-  <si>
-    <t>YLR131C</t>
-  </si>
-  <si>
-    <t>ACE2</t>
-  </si>
-  <si>
-    <t>YIL130W</t>
-  </si>
-  <si>
-    <t>ASG1</t>
-  </si>
-  <si>
-    <t>YJR060W</t>
-  </si>
-  <si>
-    <t>CBF1</t>
-  </si>
-  <si>
-    <t>YOR028C</t>
-  </si>
-  <si>
-    <t>CIN5</t>
-  </si>
-  <si>
-    <t>YBR112C</t>
-  </si>
-  <si>
-    <t>CYC8</t>
-  </si>
-  <si>
-    <t>YNL068C</t>
-  </si>
-  <si>
-    <t>FKH2</t>
-  </si>
-  <si>
-    <t>YLR013W</t>
-  </si>
-  <si>
-    <t>GAT3</t>
-  </si>
-  <si>
-    <t>YNL199C</t>
-  </si>
-  <si>
-    <t>GCR2</t>
-  </si>
-  <si>
-    <t>YER040W</t>
-  </si>
-  <si>
-    <t>GLN3</t>
-  </si>
-  <si>
-    <t>YDR174W</t>
-  </si>
-  <si>
-    <t>HMO1</t>
-  </si>
-  <si>
-    <t>YMR043W</t>
-  </si>
-  <si>
-    <t>MCM1</t>
-  </si>
-  <si>
-    <t>YGL209W</t>
-  </si>
-  <si>
-    <t>MIG2</t>
-  </si>
-  <si>
-    <t>YMR037C</t>
-  </si>
-  <si>
-    <t>MSN2</t>
-  </si>
-  <si>
-    <t>YKL062W</t>
-  </si>
-  <si>
-    <t>MSN4</t>
-  </si>
-  <si>
-    <t>YGL013C</t>
-  </si>
-  <si>
-    <t>PDR1</t>
-  </si>
-  <si>
-    <t>YNR052C</t>
-  </si>
-  <si>
-    <t>POP2</t>
-  </si>
-  <si>
-    <t>YBR275C</t>
-  </si>
-  <si>
-    <t>RIF1</t>
-  </si>
-  <si>
-    <t>YPL089C</t>
-  </si>
-  <si>
-    <t>RLM1</t>
-  </si>
-  <si>
-    <t>YLR403W</t>
-  </si>
-  <si>
-    <t>SFP1</t>
-  </si>
-  <si>
-    <t>YOR290C</t>
-  </si>
-  <si>
-    <t>SNF2</t>
-  </si>
-  <si>
-    <t>YHL025W</t>
-  </si>
-  <si>
-    <t>SNF6</t>
-  </si>
-  <si>
-    <t>YHR178W</t>
-  </si>
-  <si>
-    <t>STB5</t>
-  </si>
-  <si>
-    <t>YDR146C</t>
-  </si>
-  <si>
-    <t>SWI5</t>
-  </si>
-  <si>
-    <t>YDR451C</t>
-  </si>
-  <si>
-    <t>YHP1</t>
-  </si>
-  <si>
-    <t>YLR278C</t>
-  </si>
-  <si>
-    <t>YML027W</t>
-  </si>
-  <si>
-    <t>YOX1</t>
-  </si>
-  <si>
-    <t>YJL056C</t>
-  </si>
-  <si>
-    <t>ZAP1</t>
-  </si>
-  <si>
-    <t>DegradationRate</t>
-  </si>
-  <si>
-    <t>rows genes affected/cols genes controlling</t>
-  </si>
-  <si>
-    <t>optimization_parameter</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>alpha</t>
-  </si>
-  <si>
-    <t>kk_max</t>
-  </si>
-  <si>
-    <t>MaxIter</t>
-  </si>
-  <si>
-    <t>TolFun</t>
-  </si>
-  <si>
-    <t>MaxFunEval</t>
-  </si>
-  <si>
-    <t>TolX</t>
-  </si>
-  <si>
-    <t>Sigmoid</t>
-  </si>
-  <si>
-    <t>iestimate</t>
-  </si>
-  <si>
-    <t>igraph</t>
-  </si>
-  <si>
-    <t>fix_P</t>
-  </si>
-  <si>
-    <t>fix_b</t>
-  </si>
-  <si>
-    <t>time</t>
-  </si>
-  <si>
-    <t>Strain</t>
-  </si>
-  <si>
-    <t>wt</t>
-  </si>
-  <si>
-    <t>dcin5</t>
-  </si>
-  <si>
-    <t>Sheet</t>
-  </si>
-  <si>
-    <t>Deletion</t>
-  </si>
-  <si>
-    <t>simtime</t>
-  </si>
-  <si>
-    <t>threshold</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="10"/>
-      <name val="Verdana"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="11"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -325,38 +71,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="11">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="11">
-    <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="8" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="10" builtinId="9" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="9" builtinId="8" hidden="1"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -685,1490 +406,682 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr enableFormatConditionsCalculation="0">
-    <tabColor rgb="FFFFFFFF"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AMK28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="13" x14ac:dyDescent="0"/>
-  <cols>
-    <col min="1" max="1025" width="8.7109375" style="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:31">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="3"/>
-      <c r="AB1" s="3"/>
-      <c r="AC1" s="3"/>
-      <c r="AD1" s="3"/>
-      <c r="AE1" s="3"/>
-    </row>
-    <row r="2" spans="1:31">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>SystematicName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>StandardName</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Production_Rate</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>YLR131C</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ACE2</v>
+      </c>
+      <c r="C2">
         <f>2*degradation_rates!C2</f>
-        <v>0.46209812037329601</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="3"/>
-    </row>
-    <row r="3" spans="1:31">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3">
+        <v>0.462098120373296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>YIL130W</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ASG1</v>
+      </c>
+      <c r="C3">
         <f>2*degradation_rates!C3</f>
-        <v>5.4364483999999998E-2</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-    </row>
-    <row r="4" spans="1:31">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="3">
+        <v>0.054364484</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>YJR060W</v>
+      </c>
+      <c r="B4" t="str">
+        <v>CBF1</v>
+      </c>
+      <c r="C4">
         <f>2*degradation_rates!C4</f>
-        <v>3.6481430555786599E-2</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="3"/>
-    </row>
-    <row r="5" spans="1:31">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="3">
+        <v>0.0364814305557866</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>YOR028C</v>
+      </c>
+      <c r="B5" t="str">
+        <v>CIN5</v>
+      </c>
+      <c r="C5">
         <f>2*degradation_rates!C5</f>
-        <v>5.4364484749799602E-2</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3"/>
-    </row>
-    <row r="6" spans="1:31">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="3">
+        <v>0.0543644847497996</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>YBR112C</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CYC8</v>
+      </c>
+      <c r="C6">
         <f>2*degradation_rates!C6</f>
-        <v>5.4364483999999998E-2</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3"/>
-      <c r="AC6" s="3"/>
-      <c r="AD6" s="3"/>
-      <c r="AE6" s="3"/>
-    </row>
-    <row r="7" spans="1:31">
-      <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="3">
+        <v>0.054364484</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>YNL068C</v>
+      </c>
+      <c r="B7" t="str">
+        <v>FKH2</v>
+      </c>
+      <c r="C7">
         <f>2*degradation_rates!C7</f>
-        <v>5.3319013889226601E-2</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
-      <c r="AB7" s="3"/>
-      <c r="AC7" s="3"/>
-      <c r="AD7" s="3"/>
-      <c r="AE7" s="3"/>
-    </row>
-    <row r="8" spans="1:31">
-      <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="3">
+        <v>0.0533190138892266</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>YLR013W</v>
+      </c>
+      <c r="B8" t="str">
+        <v>GAT3</v>
+      </c>
+      <c r="C8">
         <f>2*degradation_rates!C8</f>
-        <v>5.4364484749799602E-2</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="3"/>
-      <c r="AC8" s="3"/>
-      <c r="AD8" s="3"/>
-      <c r="AE8" s="3"/>
-    </row>
-    <row r="9" spans="1:31">
-      <c r="A9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="3">
+        <v>0.0543644847497996</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>YNL199C</v>
+      </c>
+      <c r="B9" t="str">
+        <v>GCR2</v>
+      </c>
+      <c r="C9">
         <f>2*degradation_rates!C9</f>
-        <v>5.4364484749799602E-2</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
-      <c r="AB9" s="3"/>
-      <c r="AC9" s="3"/>
-      <c r="AD9" s="3"/>
-      <c r="AE9" s="3"/>
-    </row>
-    <row r="10" spans="1:31">
-      <c r="A10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="3">
+        <v>0.0543644847497996</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>YER040W</v>
+      </c>
+      <c r="B10" t="str">
+        <v>GLN3</v>
+      </c>
+      <c r="C10">
         <f>2*degradation_rates!C10</f>
-        <v>0.46209812037329601</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="3"/>
-      <c r="AB10" s="3"/>
-      <c r="AC10" s="3"/>
-      <c r="AD10" s="3"/>
-      <c r="AE10" s="3"/>
-    </row>
-    <row r="11" spans="1:31">
-      <c r="A11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="3">
+        <v>0.462098120373296</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>YDR174W</v>
+      </c>
+      <c r="B11" t="str">
+        <v>HMO1</v>
+      </c>
+      <c r="C11">
         <f>2*degradation_rates!C11</f>
-        <v>5.4364483999999998E-2</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
-      <c r="AB11" s="3"/>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="3"/>
-      <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31">
-      <c r="A12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="3">
+        <v>0.054364484</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>YMR043W</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MCM1</v>
+      </c>
+      <c r="C12">
         <f>2*degradation_rates!C12</f>
-        <v>4.6209812037329599E-3</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="3"/>
-      <c r="AB12" s="3"/>
-      <c r="AC12" s="3"/>
-      <c r="AD12" s="3"/>
-      <c r="AE12" s="3"/>
-    </row>
-    <row r="13" spans="1:31">
-      <c r="A13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="3">
+        <v>0.00462098120373296</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>YGL209W</v>
+      </c>
+      <c r="B13" t="str">
+        <v>MIG2</v>
+      </c>
+      <c r="C13">
         <f>2*degradation_rates!C13</f>
-        <v>9.2419624074659396E-2</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
-      <c r="AB13" s="3"/>
-      <c r="AC13" s="3"/>
-      <c r="AD13" s="3"/>
-      <c r="AE13" s="3"/>
-    </row>
-    <row r="14" spans="1:31">
-      <c r="A14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="3">
+        <v>0.0924196240746594</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>YMR037C</v>
+      </c>
+      <c r="B14" t="str">
+        <v>MSN2</v>
+      </c>
+      <c r="C14">
         <f>2*degradation_rates!C14</f>
-        <v>0.69314718055994595</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
-      <c r="AB14" s="3"/>
-      <c r="AC14" s="3"/>
-      <c r="AD14" s="3"/>
-      <c r="AE14" s="3"/>
-    </row>
-    <row r="15" spans="1:31">
-      <c r="A15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="3">
+        <v>0.693147180559946</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>YKL062W</v>
+      </c>
+      <c r="B15" t="str">
+        <v>MSN4</v>
+      </c>
+      <c r="C15">
         <f>2*degradation_rates!C15</f>
-        <v>5.4364484749799602E-2</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="3"/>
-      <c r="AB15" s="3"/>
-      <c r="AC15" s="3"/>
-      <c r="AD15" s="3"/>
-      <c r="AE15" s="3"/>
-    </row>
-    <row r="16" spans="1:31">
-      <c r="A16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="3">
+        <v>0.0543644847497996</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>YGL013C</v>
+      </c>
+      <c r="B16" t="str">
+        <v>PDR1</v>
+      </c>
+      <c r="C16">
         <f>2*degradation_rates!C16</f>
-        <v>5.4364484749799602E-2</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
-      <c r="AB16" s="3"/>
-      <c r="AC16" s="3"/>
-      <c r="AD16" s="3"/>
-      <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="1:31">
-      <c r="A17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="3">
+        <v>0.0543644847497996</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>YNR052C</v>
+      </c>
+      <c r="B17" t="str">
+        <v>POP2</v>
+      </c>
+      <c r="C17">
         <f>2*degradation_rates!C17</f>
-        <v>5.4364483999999998E-2</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="3"/>
-      <c r="AB17" s="3"/>
-      <c r="AC17" s="3"/>
-      <c r="AD17" s="3"/>
-      <c r="AE17" s="3"/>
-    </row>
-    <row r="18" spans="1:31">
-      <c r="A18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="3">
+        <v>0.054364484</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>YBR275C</v>
+      </c>
+      <c r="B18" t="str">
+        <v>RIF1</v>
+      </c>
+      <c r="C18">
         <f>2*degradation_rates!C18</f>
-        <v>5.4364483999999998E-2</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="3"/>
-      <c r="AB18" s="3"/>
-      <c r="AC18" s="3"/>
-      <c r="AD18" s="3"/>
-      <c r="AE18" s="3"/>
-    </row>
-    <row r="19" spans="1:31">
-      <c r="A19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="3">
+        <v>0.054364484</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>YPL089C</v>
+      </c>
+      <c r="B19" t="str">
+        <v>RLM1</v>
+      </c>
+      <c r="C19">
         <f>2*degradation_rates!C19</f>
-        <v>4.3321698784996601E-2</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
-      <c r="AB19" s="3"/>
-      <c r="AC19" s="3"/>
-      <c r="AD19" s="3"/>
-      <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="1:31">
-      <c r="A20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="3">
+        <v>0.0433216987849966</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>YLR403W</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SFP1</v>
+      </c>
+      <c r="C20">
         <f>2*degradation_rates!C20</f>
-        <v>9.2419624074659396E-2</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
-      <c r="AA20" s="3"/>
-      <c r="AB20" s="3"/>
-      <c r="AC20" s="3"/>
-      <c r="AD20" s="3"/>
-      <c r="AE20" s="3"/>
-    </row>
-    <row r="21" spans="1:31">
-      <c r="A21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="3">
+        <v>0.0924196240746594</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>YOR290C</v>
+      </c>
+      <c r="B21" t="str">
+        <v>SNF2</v>
+      </c>
+      <c r="C21">
         <f>2*degradation_rates!C21</f>
-        <v>5.4364483999999998E-2</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
-      <c r="AA21" s="3"/>
-      <c r="AB21" s="3"/>
-      <c r="AC21" s="3"/>
-      <c r="AD21" s="3"/>
-      <c r="AE21" s="3"/>
-    </row>
-    <row r="22" spans="1:31">
-      <c r="A22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="3">
+        <v>0.054364484</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>YHL025W</v>
+      </c>
+      <c r="B22" t="str">
+        <v>SNF6</v>
+      </c>
+      <c r="C22">
         <f>2*degradation_rates!C22</f>
-        <v>5.4364483999999998E-2</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="3"/>
-      <c r="AA22" s="3"/>
-      <c r="AB22" s="3"/>
-      <c r="AC22" s="3"/>
-      <c r="AD22" s="3"/>
-      <c r="AE22" s="3"/>
-    </row>
-    <row r="23" spans="1:31">
-      <c r="A23" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="3">
+        <v>0.054364484</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>YHR178W</v>
+      </c>
+      <c r="B23" t="str">
+        <v>STB5</v>
+      </c>
+      <c r="C23">
         <f>2*degradation_rates!C23</f>
-        <v>3.7467415165402397E-2</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
-      <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="3"/>
-      <c r="AA23" s="3"/>
-      <c r="AB23" s="3"/>
-      <c r="AC23" s="3"/>
-      <c r="AD23" s="3"/>
-      <c r="AE23" s="3"/>
-    </row>
-    <row r="24" spans="1:31">
-      <c r="A24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="3">
+        <v>0.0374674151654024</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>YDR146C</v>
+      </c>
+      <c r="B24" t="str">
+        <v>SWI5</v>
+      </c>
+      <c r="C24">
         <f>2*degradation_rates!C24</f>
-        <v>5.4364484749799602E-2</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="3"/>
-      <c r="AA24" s="3"/>
-      <c r="AB24" s="3"/>
-      <c r="AC24" s="3"/>
-      <c r="AD24" s="3"/>
-      <c r="AE24" s="3"/>
-    </row>
-    <row r="25" spans="1:31">
-      <c r="A25" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="3">
+        <v>0.0543644847497996</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>YDR451C</v>
+      </c>
+      <c r="B25" t="str">
+        <v>YHP1</v>
+      </c>
+      <c r="C25">
         <f>2*degradation_rates!C25</f>
-        <v>0.46209812037329601</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="3"/>
-      <c r="AA25" s="3"/>
-      <c r="AB25" s="3"/>
-      <c r="AC25" s="3"/>
-      <c r="AD25" s="3"/>
-      <c r="AE25" s="3"/>
-    </row>
-    <row r="26" spans="1:31">
-      <c r="A26" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="3">
+        <v>0.462098120373296</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>YLR278C</v>
+      </c>
+      <c r="B26" t="str">
+        <v>YLR278C</v>
+      </c>
+      <c r="C26">
         <f>2*degradation_rates!C26</f>
-        <v>5.5451774444795598E-2</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
-      <c r="Z26" s="3"/>
-      <c r="AA26" s="3"/>
-      <c r="AB26" s="3"/>
-      <c r="AC26" s="3"/>
-      <c r="AD26" s="3"/>
-      <c r="AE26" s="3"/>
-    </row>
-    <row r="27" spans="1:31">
-      <c r="A27" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="3">
+        <v>0.0554517744447956</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>YML027W</v>
+      </c>
+      <c r="B27" t="str">
+        <v>YOX1</v>
+      </c>
+      <c r="C27">
         <f>2*degradation_rates!C27</f>
-        <v>0.46209812037329601</v>
-      </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
-      <c r="Y27" s="3"/>
-      <c r="Z27" s="3"/>
-      <c r="AA27" s="3"/>
-      <c r="AB27" s="3"/>
-      <c r="AC27" s="3"/>
-      <c r="AD27" s="3"/>
-      <c r="AE27" s="3"/>
-    </row>
-    <row r="28" spans="1:31">
-      <c r="A28" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="3">
+        <v>0.462098120373296</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>YJL056C</v>
+      </c>
+      <c r="B28" t="str">
+        <v>ZAP1</v>
+      </c>
+      <c r="C28">
         <f>2*degradation_rates!C28</f>
-        <v>8.5048733811036205E-3</v>
-      </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="3"/>
-      <c r="AA28" s="3"/>
-      <c r="AB28" s="3"/>
-      <c r="AC28" s="3"/>
-      <c r="AD28" s="3"/>
-      <c r="AE28" s="3"/>
+        <v>0.00850487338110362</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:AMK28"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr enableFormatConditionsCalculation="0">
-    <tabColor rgb="FFFFFFFF"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AMK28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="13" x14ac:dyDescent="0"/>
-  <cols>
-    <col min="1" max="1025" width="8.7109375" style="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>SystematicName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>StandardName</v>
+      </c>
+      <c r="C1" t="str">
+        <v>DegradationRate</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>YLR131C</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ACE2</v>
+      </c>
+      <c r="C2">
         <v>0.231049060186648</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2.7182241999999999E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1.82407152778933E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2.7182242374899801E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2">
-        <v>2.7182241999999999E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2.66595069446133E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2.7182242374899801E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2.7182242374899801E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="2">
+    <row r="3">
+      <c r="A3" t="str">
+        <v>YIL130W</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ASG1</v>
+      </c>
+      <c r="C3">
+        <v>0.027182242</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>YJR060W</v>
+      </c>
+      <c r="B4" t="str">
+        <v>CBF1</v>
+      </c>
+      <c r="C4">
+        <v>0.0182407152778933</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>YOR028C</v>
+      </c>
+      <c r="B5" t="str">
+        <v>CIN5</v>
+      </c>
+      <c r="C5">
+        <v>0.0271822423748998</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>YBR112C</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CYC8</v>
+      </c>
+      <c r="C6">
+        <v>0.027182242</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>YNL068C</v>
+      </c>
+      <c r="B7" t="str">
+        <v>FKH2</v>
+      </c>
+      <c r="C7">
+        <v>0.0266595069446133</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>YLR013W</v>
+      </c>
+      <c r="B8" t="str">
+        <v>GAT3</v>
+      </c>
+      <c r="C8">
+        <v>0.0271822423748998</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>YNL199C</v>
+      </c>
+      <c r="B9" t="str">
+        <v>GCR2</v>
+      </c>
+      <c r="C9">
+        <v>0.0271822423748998</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>YER040W</v>
+      </c>
+      <c r="B10" t="str">
+        <v>GLN3</v>
+      </c>
+      <c r="C10">
         <v>0.231049060186648</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2.7182241999999999E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="2">
-        <v>2.3104906018664799E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="2">
-        <v>4.6209812037329698E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="2">
-        <v>0.34657359027997298</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="2">
-        <v>2.7182242374899801E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="2">
-        <v>2.7182242374899801E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="2">
-        <v>2.7182241999999999E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="2">
-        <v>2.7182241999999999E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="2">
-        <v>2.1660849392498301E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="2">
-        <v>4.6209812037329698E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="2">
-        <v>2.7182241999999999E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="2">
-        <v>2.7182241999999999E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="2">
-        <v>1.8733707582701199E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="2">
-        <v>2.7182242374899801E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="2">
+    <row r="11">
+      <c r="A11" t="str">
+        <v>YDR174W</v>
+      </c>
+      <c r="B11" t="str">
+        <v>HMO1</v>
+      </c>
+      <c r="C11">
+        <v>0.027182242</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>YMR043W</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MCM1</v>
+      </c>
+      <c r="C12">
+        <v>0.00231049060186648</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>YGL209W</v>
+      </c>
+      <c r="B13" t="str">
+        <v>MIG2</v>
+      </c>
+      <c r="C13">
+        <v>0.0462098120373297</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>YMR037C</v>
+      </c>
+      <c r="B14" t="str">
+        <v>MSN2</v>
+      </c>
+      <c r="C14">
+        <v>0.346573590279973</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>YKL062W</v>
+      </c>
+      <c r="B15" t="str">
+        <v>MSN4</v>
+      </c>
+      <c r="C15">
+        <v>0.0271822423748998</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>YGL013C</v>
+      </c>
+      <c r="B16" t="str">
+        <v>PDR1</v>
+      </c>
+      <c r="C16">
+        <v>0.0271822423748998</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>YNR052C</v>
+      </c>
+      <c r="B17" t="str">
+        <v>POP2</v>
+      </c>
+      <c r="C17">
+        <v>0.027182242</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>YBR275C</v>
+      </c>
+      <c r="B18" t="str">
+        <v>RIF1</v>
+      </c>
+      <c r="C18">
+        <v>0.027182242</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>YPL089C</v>
+      </c>
+      <c r="B19" t="str">
+        <v>RLM1</v>
+      </c>
+      <c r="C19">
+        <v>0.0216608493924983</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>YLR403W</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SFP1</v>
+      </c>
+      <c r="C20">
+        <v>0.0462098120373297</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>YOR290C</v>
+      </c>
+      <c r="B21" t="str">
+        <v>SNF2</v>
+      </c>
+      <c r="C21">
+        <v>0.027182242</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>YHL025W</v>
+      </c>
+      <c r="B22" t="str">
+        <v>SNF6</v>
+      </c>
+      <c r="C22">
+        <v>0.027182242</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>YHR178W</v>
+      </c>
+      <c r="B23" t="str">
+        <v>STB5</v>
+      </c>
+      <c r="C23">
+        <v>0.0187337075827012</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>YDR146C</v>
+      </c>
+      <c r="B24" t="str">
+        <v>SWI5</v>
+      </c>
+      <c r="C24">
+        <v>0.0271822423748998</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>YDR451C</v>
+      </c>
+      <c r="B25" t="str">
+        <v>YHP1</v>
+      </c>
+      <c r="C25">
         <v>0.231049060186648</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="2">
-        <v>2.7725887222397799E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="2">
+    <row r="26">
+      <c r="A26" t="str">
+        <v>YLR278C</v>
+      </c>
+      <c r="B26" t="str">
+        <v>YLR278C</v>
+      </c>
+      <c r="C26">
+        <v>0.0277258872223978</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>YML027W</v>
+      </c>
+      <c r="B27" t="str">
+        <v>YOX1</v>
+      </c>
+      <c r="C27">
         <v>0.231049060186648</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="2">
-        <v>4.2524366905518102E-3</v>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>YJL056C</v>
+      </c>
+      <c r="B28" t="str">
+        <v>ZAP1</v>
+      </c>
+      <c r="C28">
+        <v>0.00425243669055181</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:AMK28"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr enableFormatConditionsCalculation="0">
-    <tabColor rgb="FFFFFFFF"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="13" x14ac:dyDescent="0"/>
   <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>SystematicName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>StandardName</v>
       </c>
       <c r="C1">
         <v>15</v>
@@ -2210,42 +1123,42 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>YLR131C</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ACE2</v>
       </c>
       <c r="C2">
-        <v>0.60560000000000003</v>
+        <v>0.6056</v>
       </c>
       <c r="D2">
-        <v>-1.0571999999999999</v>
+        <v>-1.0572</v>
       </c>
       <c r="E2">
-        <v>0.16569999999999999</v>
+        <v>0.1657</v>
       </c>
       <c r="F2">
-        <v>-0.38440000000000002</v>
+        <v>-0.3844</v>
       </c>
       <c r="G2">
-        <v>0.55430000000000001</v>
+        <v>0.5543</v>
       </c>
       <c r="H2">
         <v>0.9244</v>
       </c>
       <c r="I2">
-        <v>-0.38990000000000002</v>
+        <v>-0.3899</v>
       </c>
       <c r="J2">
-        <v>-0.60240000000000005</v>
+        <v>-0.6024</v>
       </c>
       <c r="K2">
-        <v>0.31380000000000002</v>
+        <v>0.3138</v>
       </c>
       <c r="L2">
-        <v>0.79830000000000001</v>
+        <v>0.7983</v>
       </c>
       <c r="M2">
         <v>0.5161</v>
@@ -2257,112 +1170,112 @@
         <v>-1.2202</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>YIL130W</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ASG1</v>
       </c>
       <c r="C3">
         <v>-0.3261</v>
       </c>
       <c r="D3">
-        <v>7.8E-2</v>
+        <v>0.078</v>
       </c>
       <c r="E3">
-        <v>-0.84089999999999998</v>
+        <v>-0.8409</v>
       </c>
       <c r="F3">
         <v>-0.2636</v>
       </c>
       <c r="G3">
-        <v>-0.47970000000000002</v>
+        <v>-0.4797</v>
       </c>
       <c r="H3">
-        <v>1.7999999999999999E-2</v>
+        <v>0.018</v>
       </c>
       <c r="I3">
-        <v>0.24590000000000001</v>
+        <v>0.2459</v>
       </c>
       <c r="J3">
-        <v>0.42809999999999998</v>
+        <v>0.4281</v>
       </c>
       <c r="K3">
-        <v>0.99270000000000003</v>
+        <v>0.9927</v>
       </c>
       <c r="L3">
-        <v>-0.68279999999999996</v>
+        <v>-0.6828</v>
       </c>
       <c r="M3">
-        <v>-0.64070000000000005</v>
+        <v>-0.6407</v>
       </c>
       <c r="N3">
-        <v>-0.70350000000000001</v>
+        <v>-0.7035</v>
       </c>
       <c r="O3">
-        <v>0.64600000000000002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>0.646</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>YJR060W</v>
+      </c>
+      <c r="B4" t="str">
+        <v>CBF1</v>
       </c>
       <c r="C4">
         <v>-1.2483</v>
       </c>
       <c r="D4">
-        <v>-2.2669000000000001</v>
+        <v>-2.2669</v>
       </c>
       <c r="E4">
-        <v>0.27729999999999999</v>
+        <v>0.2773</v>
       </c>
       <c r="F4">
-        <v>-0.51549999999999996</v>
+        <v>-0.5155</v>
       </c>
       <c r="G4">
         <v>-1.4641</v>
       </c>
       <c r="H4">
-        <v>-1.0431999999999999</v>
+        <v>-1.0432</v>
       </c>
       <c r="I4">
-        <v>-1.9531000000000001</v>
+        <v>-1.9531</v>
       </c>
       <c r="J4">
-        <v>0.26069999999999999</v>
+        <v>0.2607</v>
       </c>
       <c r="K4">
-        <v>-0.28639999999999999</v>
+        <v>-0.2864</v>
       </c>
       <c r="L4">
         <v>-1.8126</v>
       </c>
       <c r="M4">
-        <v>-0.73309999999999997</v>
+        <v>-0.7331</v>
       </c>
       <c r="N4">
         <v>-1.8591</v>
       </c>
       <c r="O4">
-        <v>-9.98E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>-0.0998</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>YOR028C</v>
+      </c>
+      <c r="B5" t="str">
+        <v>CIN5</v>
       </c>
       <c r="C5">
-        <v>-0.16739999999999999</v>
+        <v>-0.1674</v>
       </c>
       <c r="D5">
-        <v>-9.5899999999999999E-2</v>
+        <v>-0.0959</v>
       </c>
       <c r="E5">
         <v>1.202</v>
@@ -2371,7 +1284,7 @@
         <v>1.3568</v>
       </c>
       <c r="G5">
-        <v>-0.42530000000000001</v>
+        <v>-0.4253</v>
       </c>
       <c r="H5">
         <v>0.4803</v>
@@ -2380,51 +1293,51 @@
         <v>1.0042</v>
       </c>
       <c r="J5">
-        <v>1.2911999999999999</v>
+        <v>1.2912</v>
       </c>
       <c r="K5">
-        <v>2.1520000000000001</v>
+        <v>2.152</v>
       </c>
       <c r="L5">
-        <v>2.1587000000000001</v>
+        <v>2.1587</v>
       </c>
       <c r="M5">
-        <v>0.86670000000000003</v>
+        <v>0.8667</v>
       </c>
       <c r="N5">
-        <v>2.4531000000000001</v>
+        <v>2.4531</v>
       </c>
       <c r="O5">
-        <v>1.5551999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>1.5552</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>YBR112C</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CYC8</v>
       </c>
       <c r="C6">
         <v>-0.3871</v>
       </c>
       <c r="D6">
-        <v>0.33900000000000002</v>
+        <v>0.339</v>
       </c>
       <c r="E6">
-        <v>-0.48409999999999997</v>
+        <v>-0.4841</v>
       </c>
       <c r="F6">
         <v>-0.4753</v>
       </c>
       <c r="G6">
-        <v>0.54179999999999995</v>
+        <v>0.5418</v>
       </c>
       <c r="H6">
-        <v>0.21110000000000001</v>
+        <v>0.2111</v>
       </c>
       <c r="I6">
-        <v>3.4200000000000001E-2</v>
+        <v>0.0342</v>
       </c>
       <c r="J6">
         <v>0.4803</v>
@@ -2433,139 +1346,139 @@
         <v>-1.2919</v>
       </c>
       <c r="L6">
-        <v>0.34670000000000001</v>
+        <v>0.3467</v>
       </c>
       <c r="M6">
-        <v>-3.32E-2</v>
+        <v>-0.0332</v>
       </c>
       <c r="N6">
-        <v>-0.15540000000000001</v>
+        <v>-0.1554</v>
       </c>
       <c r="O6">
-        <v>0.60240000000000005</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>14</v>
+        <v>0.6024</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>YNL068C</v>
+      </c>
+      <c r="B7" t="str">
+        <v>FKH2</v>
       </c>
       <c r="C7">
-        <v>-0.44940000000000002</v>
+        <v>-0.4494</v>
       </c>
       <c r="D7">
-        <v>-0.53610000000000002</v>
+        <v>-0.5361</v>
       </c>
       <c r="E7">
-        <v>0.19420000000000001</v>
+        <v>0.1942</v>
       </c>
       <c r="F7">
         <v>-0.4073</v>
       </c>
       <c r="G7">
-        <v>8.8000000000000005E-3</v>
+        <v>0.0088</v>
       </c>
       <c r="H7">
-        <v>-0.18840000000000001</v>
+        <v>-0.1884</v>
       </c>
       <c r="I7">
-        <v>-1.7910999999999999</v>
+        <v>-1.7911</v>
       </c>
       <c r="J7">
-        <v>-0.20610000000000001</v>
+        <v>-0.2061</v>
       </c>
       <c r="K7">
-        <v>-0.78349999999999997</v>
+        <v>-0.7835</v>
       </c>
       <c r="L7">
-        <v>-0.96879999999999999</v>
+        <v>-0.9688</v>
       </c>
       <c r="M7">
         <v>-0.7742</v>
       </c>
       <c r="N7">
-        <v>-0.91649999999999998</v>
+        <v>-0.9165</v>
       </c>
       <c r="O7">
-        <v>-0.70030000000000003</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>-0.7003</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>YLR013W</v>
+      </c>
+      <c r="B8" t="str">
+        <v>GAT3</v>
       </c>
       <c r="C8">
         <v>0.1002</v>
       </c>
       <c r="D8">
-        <v>-0.18679999999999999</v>
+        <v>-0.1868</v>
       </c>
       <c r="E8">
         <v>1.456</v>
       </c>
       <c r="F8">
-        <v>1.4429000000000001</v>
+        <v>1.4429</v>
       </c>
       <c r="G8">
-        <v>-8.9200000000000002E-2</v>
+        <v>-0.0892</v>
       </c>
       <c r="H8">
         <v>-0.1139</v>
       </c>
       <c r="I8">
-        <v>0.87050000000000005</v>
+        <v>0.8705</v>
       </c>
       <c r="J8">
         <v>1.0566</v>
       </c>
       <c r="K8">
-        <v>1.0895999999999999</v>
+        <v>1.0896</v>
       </c>
       <c r="L8">
-        <v>0.50770000000000004</v>
+        <v>0.5077</v>
       </c>
       <c r="M8">
-        <v>-0.25840000000000002</v>
+        <v>-0.2584</v>
       </c>
       <c r="N8">
-        <v>0.82450000000000001</v>
+        <v>0.8245</v>
       </c>
       <c r="O8">
         <v>0.1353</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>18</v>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>YNL199C</v>
+      </c>
+      <c r="B9" t="str">
+        <v>GCR2</v>
       </c>
       <c r="C9">
-        <v>0.53239999999999998</v>
+        <v>0.5324</v>
       </c>
       <c r="D9">
-        <v>0.86529999999999996</v>
+        <v>0.8653</v>
       </c>
       <c r="E9">
         <v>-0.1229</v>
       </c>
       <c r="F9">
-        <v>-1.1520999999999999</v>
+        <v>-1.1521</v>
       </c>
       <c r="G9">
-        <v>0.42320000000000002</v>
+        <v>0.4232</v>
       </c>
       <c r="H9">
-        <v>0.82010000000000005</v>
+        <v>0.8201</v>
       </c>
       <c r="I9">
-        <v>9.3399999999999997E-2</v>
+        <v>0.0934</v>
       </c>
       <c r="J9">
         <v>-0.3362</v>
@@ -2574,74 +1487,74 @@
         <v>-0.2999</v>
       </c>
       <c r="L9">
-        <v>-0.30709999999999998</v>
+        <v>-0.3071</v>
       </c>
       <c r="M9">
-        <v>-0.56789999999999996</v>
+        <v>-0.5679</v>
       </c>
       <c r="N9">
-        <v>-0.91559999999999997</v>
+        <v>-0.9156</v>
       </c>
       <c r="O9">
-        <v>-0.36509999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>20</v>
+        <v>-0.3651</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>YER040W</v>
+      </c>
+      <c r="B10" t="str">
+        <v>GLN3</v>
       </c>
       <c r="C10">
-        <v>-1.2251000000000001</v>
+        <v>-1.2251</v>
       </c>
       <c r="D10">
         <v>0.3775</v>
       </c>
       <c r="E10">
-        <v>0.16650000000000001</v>
+        <v>0.1665</v>
       </c>
       <c r="F10">
-        <v>-0.54879999999999995</v>
+        <v>-0.5488</v>
       </c>
       <c r="G10">
-        <v>-0.64390000000000003</v>
+        <v>-0.6439</v>
       </c>
       <c r="H10">
         <v>-0.2681</v>
       </c>
       <c r="I10">
-        <v>1.4159999999999999</v>
+        <v>1.416</v>
       </c>
       <c r="J10">
-        <v>0.99670000000000003</v>
+        <v>0.9967</v>
       </c>
       <c r="K10">
-        <v>0.73699999999999999</v>
+        <v>0.737</v>
       </c>
       <c r="L10">
         <v>0.1993</v>
       </c>
       <c r="M10">
-        <v>0.83379999999999999</v>
+        <v>0.8338</v>
       </c>
       <c r="N10">
         <v>0.8669</v>
       </c>
       <c r="O10">
-        <v>0.19270000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>22</v>
+        <v>0.1927</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>YDR174W</v>
+      </c>
+      <c r="B11" t="str">
+        <v>HMO1</v>
       </c>
       <c r="C11">
-        <v>0.30840000000000001</v>
+        <v>0.3084</v>
       </c>
       <c r="D11">
         <v>0.2238</v>
@@ -2650,7 +1563,7 @@
         <v>1.6832</v>
       </c>
       <c r="F11">
-        <v>1.1787000000000001</v>
+        <v>1.1787</v>
       </c>
       <c r="G11">
         <v>-0.88</v>
@@ -2662,124 +1575,124 @@
         <v>1.2038</v>
       </c>
       <c r="J11">
-        <v>1.1176999999999999</v>
+        <v>1.1177</v>
       </c>
       <c r="K11">
-        <v>1.7827999999999999</v>
+        <v>1.7828</v>
       </c>
       <c r="L11">
         <v>1.4458</v>
       </c>
       <c r="M11">
-        <v>0.86680000000000001</v>
+        <v>0.8668</v>
       </c>
       <c r="N11">
-        <v>1.6827000000000001</v>
+        <v>1.6827</v>
       </c>
       <c r="O11">
-        <v>2.0472999999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>24</v>
+        <v>2.0473</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>YMR043W</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MCM1</v>
       </c>
       <c r="C12">
         <v>-2.0259</v>
       </c>
       <c r="D12">
-        <v>1.2025999999999999</v>
+        <v>1.2026</v>
       </c>
       <c r="E12">
-        <v>0.85219999999999996</v>
+        <v>0.8522</v>
       </c>
       <c r="F12">
         <v>1.111</v>
       </c>
       <c r="G12">
-        <v>-0.42909999999999998</v>
+        <v>-0.4291</v>
       </c>
       <c r="H12">
-        <v>-0.88849999999999996</v>
+        <v>-0.8885</v>
       </c>
       <c r="I12">
-        <v>0.93540000000000001</v>
+        <v>0.9354</v>
       </c>
       <c r="J12">
         <v>0.7026</v>
       </c>
       <c r="K12">
-        <v>1.2608999999999999</v>
+        <v>1.2609</v>
       </c>
       <c r="L12">
-        <v>-0.17230000000000001</v>
+        <v>-0.1723</v>
       </c>
       <c r="M12">
-        <v>-0.83009999999999995</v>
+        <v>-0.8301</v>
       </c>
       <c r="N12">
-        <v>1.1946000000000001</v>
+        <v>1.1946</v>
       </c>
       <c r="O12">
-        <v>0.24709999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>26</v>
+        <v>0.2471</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>YGL209W</v>
+      </c>
+      <c r="B13" t="str">
+        <v>MIG2</v>
       </c>
       <c r="C13">
-        <v>3.0510999999999999</v>
+        <v>3.0511</v>
       </c>
       <c r="D13">
-        <v>8.6073000000000004</v>
+        <v>8.6073</v>
       </c>
       <c r="E13">
-        <v>5.3079000000000001</v>
+        <v>5.3079</v>
       </c>
       <c r="F13">
-        <v>3.3574000000000002</v>
+        <v>3.3574</v>
       </c>
       <c r="G13">
-        <v>2.6960000000000002</v>
+        <v>2.696</v>
       </c>
       <c r="H13">
-        <v>0.59260000000000002</v>
+        <v>0.5926</v>
       </c>
       <c r="I13">
         <v>2.8308</v>
       </c>
       <c r="J13">
-        <v>0.84670000000000001</v>
+        <v>0.8467</v>
       </c>
       <c r="K13">
-        <v>-0.64390000000000003</v>
+        <v>-0.6439</v>
       </c>
       <c r="L13">
-        <v>-0.91930000000000001</v>
+        <v>-0.9193</v>
       </c>
       <c r="M13">
-        <v>-2.3355999999999999</v>
+        <v>-2.3356</v>
       </c>
       <c r="N13">
         <v>-1.7196</v>
       </c>
       <c r="O13">
-        <v>-1.7269000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>28</v>
+        <v>-1.7269</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>YMR037C</v>
+      </c>
+      <c r="B14" t="str">
+        <v>MSN2</v>
       </c>
       <c r="C14">
         <v>-1.0323</v>
@@ -2788,392 +1701,392 @@
         <v>1.0141</v>
       </c>
       <c r="E14">
-        <v>0.20569999999999999</v>
+        <v>0.2057</v>
       </c>
       <c r="F14">
         <v>-0.2848</v>
       </c>
       <c r="G14">
-        <v>0.33500000000000002</v>
+        <v>0.335</v>
       </c>
       <c r="H14">
-        <v>0.84209999999999996</v>
+        <v>0.8421</v>
       </c>
       <c r="I14">
-        <v>0.13189999999999999</v>
+        <v>0.1319</v>
       </c>
       <c r="J14">
         <v>1.4536</v>
       </c>
       <c r="K14">
-        <v>-0.76559999999999995</v>
+        <v>-0.7656</v>
       </c>
       <c r="L14">
-        <v>0.74419999999999997</v>
+        <v>0.7442</v>
       </c>
       <c r="M14">
         <v>1.2458</v>
       </c>
       <c r="N14">
-        <v>0.87539999999999996</v>
+        <v>0.8754</v>
       </c>
       <c r="O14">
         <v>-0.1343</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>30</v>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>YKL062W</v>
+      </c>
+      <c r="B15" t="str">
+        <v>MSN4</v>
       </c>
       <c r="C15">
         <v>-1.3305</v>
       </c>
       <c r="D15">
-        <v>2.5337000000000001</v>
+        <v>2.5337</v>
       </c>
       <c r="E15">
-        <v>1.4569000000000001</v>
+        <v>1.4569</v>
       </c>
       <c r="F15">
         <v>1.2762</v>
       </c>
       <c r="G15">
-        <v>0.65349999999999997</v>
+        <v>0.6535</v>
       </c>
       <c r="H15">
         <v>0.9839</v>
       </c>
       <c r="I15">
-        <v>2.1579999999999999</v>
+        <v>2.158</v>
       </c>
       <c r="J15">
-        <v>-0.51170000000000004</v>
+        <v>-0.5117</v>
       </c>
       <c r="K15">
-        <v>1.6001000000000001</v>
+        <v>1.6001</v>
       </c>
       <c r="L15">
-        <v>2.2101999999999999</v>
+        <v>2.2102</v>
       </c>
       <c r="M15">
-        <v>0.93799999999999994</v>
+        <v>0.938</v>
       </c>
       <c r="N15">
         <v>2.6795</v>
       </c>
       <c r="O15">
-        <v>-6.08E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>32</v>
+        <v>-0.0608</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>YGL013C</v>
+      </c>
+      <c r="B16" t="str">
+        <v>PDR1</v>
       </c>
       <c r="C16">
-        <v>-2.3953000000000002</v>
+        <v>-2.3953</v>
       </c>
       <c r="D16">
-        <v>-0.60880000000000001</v>
+        <v>-0.6088</v>
       </c>
       <c r="E16">
-        <v>-1.1042000000000001</v>
+        <v>-1.1042</v>
       </c>
       <c r="F16">
-        <v>-0.98609999999999998</v>
+        <v>-0.9861</v>
       </c>
       <c r="G16">
-        <v>-1.0640000000000001</v>
+        <v>-1.064</v>
       </c>
       <c r="H16">
-        <v>0.55830000000000002</v>
+        <v>0.5583</v>
       </c>
       <c r="I16">
-        <v>-2.8999999999999998E-3</v>
+        <v>-0.0029</v>
       </c>
       <c r="J16">
-        <v>-0.82210000000000005</v>
+        <v>-0.8221</v>
       </c>
       <c r="K16">
-        <v>-0.40250000000000002</v>
+        <v>-0.4025</v>
       </c>
       <c r="L16">
-        <v>0.29139999999999999</v>
+        <v>0.2914</v>
       </c>
       <c r="M16">
-        <v>-1.9228000000000001</v>
+        <v>-1.9228</v>
       </c>
       <c r="N16">
-        <v>-1.1823999999999999</v>
+        <v>-1.1824</v>
       </c>
       <c r="O16">
-        <v>0.55130000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
-      <c r="A17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>34</v>
+        <v>0.5513</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>YNR052C</v>
+      </c>
+      <c r="B17" t="str">
+        <v>POP2</v>
       </c>
       <c r="C17">
-        <v>1.7509999999999999</v>
+        <v>1.751</v>
       </c>
       <c r="D17">
         <v>1.458</v>
       </c>
       <c r="E17">
-        <v>1.2230000000000001</v>
+        <v>1.223</v>
       </c>
       <c r="F17">
-        <v>0.44879999999999998</v>
+        <v>0.4488</v>
       </c>
       <c r="G17">
-        <v>1.9444999999999999</v>
+        <v>1.9445</v>
       </c>
       <c r="H17">
         <v>1.1408</v>
       </c>
       <c r="I17">
-        <v>1.6639999999999999</v>
+        <v>1.664</v>
       </c>
       <c r="J17">
-        <v>1.3938999999999999</v>
+        <v>1.3939</v>
       </c>
       <c r="K17">
         <v>-0.2243</v>
       </c>
       <c r="L17">
-        <v>0.98570000000000002</v>
+        <v>0.9857</v>
       </c>
       <c r="M17">
-        <v>0.77959999999999996</v>
+        <v>0.7796</v>
       </c>
       <c r="N17">
-        <v>1.3052999999999999</v>
+        <v>1.3053</v>
       </c>
       <c r="O17">
-        <v>0.71079999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
-      <c r="A18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>36</v>
+        <v>0.7108</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>YBR275C</v>
+      </c>
+      <c r="B18" t="str">
+        <v>RIF1</v>
       </c>
       <c r="C18">
-        <v>0.82110000000000005</v>
+        <v>0.8211</v>
       </c>
       <c r="D18">
-        <v>0.64070000000000005</v>
+        <v>0.6407</v>
       </c>
       <c r="E18">
         <v>1.353</v>
       </c>
       <c r="F18">
-        <v>-0.14330000000000001</v>
+        <v>-0.1433</v>
       </c>
       <c r="G18">
-        <v>-2.2048999999999999</v>
+        <v>-2.2049</v>
       </c>
       <c r="H18">
-        <v>-1.5176000000000001</v>
+        <v>-1.5176</v>
       </c>
       <c r="I18">
-        <v>0.70979999999999999</v>
+        <v>0.7098</v>
       </c>
       <c r="J18">
-        <v>0.91290000000000004</v>
+        <v>0.9129</v>
       </c>
       <c r="K18">
-        <v>8.8000000000000005E-3</v>
+        <v>0.0088</v>
       </c>
       <c r="L18">
-        <v>-0.42049999999999998</v>
+        <v>-0.4205</v>
       </c>
       <c r="M18">
-        <v>-1.0754999999999999</v>
+        <v>-1.0755</v>
       </c>
       <c r="N18">
-        <v>0.78590000000000004</v>
+        <v>0.7859</v>
       </c>
       <c r="O18">
-        <v>0.84750000000000003</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
-      <c r="A19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>38</v>
+        <v>0.8475</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>YPL089C</v>
+      </c>
+      <c r="B19" t="str">
+        <v>RLM1</v>
       </c>
       <c r="C19">
         <v>2.4135</v>
       </c>
       <c r="D19">
-        <v>1.0065999999999999</v>
+        <v>1.0066</v>
       </c>
       <c r="E19">
-        <v>-0.67900000000000005</v>
+        <v>-0.679</v>
       </c>
       <c r="F19">
-        <v>0.15670000000000001</v>
+        <v>0.1567</v>
       </c>
       <c r="G19">
-        <v>0.74199999999999999</v>
+        <v>0.742</v>
       </c>
       <c r="H19">
         <v>2.0768</v>
       </c>
       <c r="I19">
-        <v>1.8876999999999999</v>
+        <v>1.8877</v>
       </c>
       <c r="J19">
-        <v>-0.60099999999999998</v>
+        <v>-0.601</v>
       </c>
       <c r="K19">
-        <v>0.26119999999999999</v>
+        <v>0.2612</v>
       </c>
       <c r="L19">
-        <v>0.80259999999999998</v>
+        <v>0.8026</v>
       </c>
       <c r="M19">
         <v>1.8047</v>
       </c>
       <c r="N19">
-        <v>0.72909999999999997</v>
+        <v>0.7291</v>
       </c>
       <c r="O19">
-        <v>-0.56440000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>40</v>
+        <v>-0.5644</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>YLR403W</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SFP1</v>
       </c>
       <c r="C20">
-        <v>4.02E-2</v>
+        <v>0.0402</v>
       </c>
       <c r="D20">
-        <v>2.0834000000000001</v>
+        <v>2.0834</v>
       </c>
       <c r="E20">
-        <v>1.3482000000000001</v>
+        <v>1.3482</v>
       </c>
       <c r="F20">
-        <v>-0.48020000000000002</v>
+        <v>-0.4802</v>
       </c>
       <c r="G20">
-        <v>0.66820000000000002</v>
+        <v>0.6682</v>
       </c>
       <c r="H20">
         <v>0.4582</v>
       </c>
       <c r="I20">
-        <v>2.1783999999999999</v>
+        <v>2.1784</v>
       </c>
       <c r="J20">
-        <v>-0.92569999999999997</v>
+        <v>-0.9257</v>
       </c>
       <c r="K20">
-        <v>0.90169999999999995</v>
+        <v>0.9017</v>
       </c>
       <c r="L20">
         <v>1.3484</v>
       </c>
       <c r="M20">
-        <v>0.90249999999999997</v>
+        <v>0.9025</v>
       </c>
       <c r="N20">
-        <v>0.85019999999999996</v>
+        <v>0.8502</v>
       </c>
       <c r="O20">
         <v>-1.0747</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
-      <c r="A21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>42</v>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>YOR290C</v>
+      </c>
+      <c r="B21" t="str">
+        <v>SNF2</v>
       </c>
       <c r="C21">
         <v>-1.5927</v>
       </c>
       <c r="D21">
-        <v>-0.74270000000000003</v>
+        <v>-0.7427</v>
       </c>
       <c r="E21">
-        <v>0.27689999999999998</v>
+        <v>0.2769</v>
       </c>
       <c r="F21">
-        <v>0.40739999999999998</v>
+        <v>0.4074</v>
       </c>
       <c r="G21">
-        <v>-0.26860000000000001</v>
+        <v>-0.2686</v>
       </c>
       <c r="H21">
         <v>-1.0198</v>
       </c>
       <c r="I21">
-        <v>-5.9900000000000002E-2</v>
+        <v>-0.0599</v>
       </c>
       <c r="J21">
-        <v>-0.44209999999999999</v>
+        <v>-0.4421</v>
       </c>
       <c r="K21">
-        <v>-0.48609999999999998</v>
+        <v>-0.4861</v>
       </c>
       <c r="L21">
-        <v>0.36580000000000001</v>
+        <v>0.3658</v>
       </c>
       <c r="M21">
         <v>-0.7752</v>
       </c>
       <c r="N21">
-        <v>-0.41930000000000001</v>
+        <v>-0.4193</v>
       </c>
       <c r="O21">
-        <v>0.37980000000000003</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>44</v>
+        <v>0.3798</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>YHL025W</v>
+      </c>
+      <c r="B22" t="str">
+        <v>SNF6</v>
       </c>
       <c r="C22">
-        <v>-0.10249999999999999</v>
+        <v>-0.1025</v>
       </c>
       <c r="D22">
-        <v>0.17269999999999999</v>
+        <v>0.1727</v>
       </c>
       <c r="E22">
-        <v>2.5152000000000001</v>
+        <v>2.5152</v>
       </c>
       <c r="F22">
-        <v>0.90259999999999996</v>
+        <v>0.9026</v>
       </c>
       <c r="G22">
-        <v>-1.2200000000000001E-2</v>
+        <v>-0.0122</v>
       </c>
       <c r="H22">
-        <v>0.17480000000000001</v>
+        <v>0.1748</v>
       </c>
       <c r="I22">
         <v>0.2737</v>
@@ -3182,39 +2095,39 @@
         <v>1.8976</v>
       </c>
       <c r="K22">
-        <v>0.97670000000000001</v>
+        <v>0.9767</v>
       </c>
       <c r="L22">
         <v>0.18</v>
       </c>
       <c r="M22">
-        <v>0.50419999999999998</v>
+        <v>0.5042</v>
       </c>
       <c r="N22">
-        <v>7.6399999999999996E-2</v>
+        <v>0.0764</v>
       </c>
       <c r="O22">
-        <v>-1.3151999999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="A23" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>46</v>
+        <v>-1.3152</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>YHR178W</v>
+      </c>
+      <c r="B23" t="str">
+        <v>STB5</v>
       </c>
       <c r="C23">
-        <v>-1.7184999999999999</v>
+        <v>-1.7185</v>
       </c>
       <c r="D23">
         <v>-0.4859</v>
       </c>
       <c r="E23">
-        <v>0.34960000000000002</v>
+        <v>0.3496</v>
       </c>
       <c r="F23">
-        <v>-0.13120000000000001</v>
+        <v>-0.1312</v>
       </c>
       <c r="G23">
         <v>-2.4129</v>
@@ -3223,57 +2136,57 @@
         <v>-2.1711</v>
       </c>
       <c r="I23">
-        <v>0.50839999999999996</v>
+        <v>0.5084</v>
       </c>
       <c r="J23">
-        <v>7.8600000000000003E-2</v>
+        <v>0.0786</v>
       </c>
       <c r="K23">
-        <v>3.27E-2</v>
+        <v>0.0327</v>
       </c>
       <c r="L23">
-        <v>-1.3431999999999999</v>
+        <v>-1.3432</v>
       </c>
       <c r="M23">
-        <v>-2.6659000000000002</v>
+        <v>-2.6659</v>
       </c>
       <c r="N23">
-        <v>0.18840000000000001</v>
+        <v>0.1884</v>
       </c>
       <c r="O23">
         <v>-0.2757</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>48</v>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>YDR146C</v>
+      </c>
+      <c r="B24" t="str">
+        <v>SWI5</v>
       </c>
       <c r="C24">
-        <v>-0.73870000000000002</v>
+        <v>-0.7387</v>
       </c>
       <c r="D24">
-        <v>-0.20230000000000001</v>
+        <v>-0.2023</v>
       </c>
       <c r="E24">
-        <v>-0.93069999999999997</v>
+        <v>-0.9307</v>
       </c>
       <c r="F24">
-        <v>-0.73119999999999996</v>
+        <v>-0.7312</v>
       </c>
       <c r="G24">
         <v>-1.806</v>
       </c>
       <c r="H24">
-        <v>0.73560000000000003</v>
+        <v>0.7356</v>
       </c>
       <c r="I24">
-        <v>-0.25230000000000002</v>
+        <v>-0.2523</v>
       </c>
       <c r="J24">
-        <v>-0.16300000000000001</v>
+        <v>-0.163</v>
       </c>
       <c r="K24">
         <v>-1.0767</v>
@@ -3282,174 +2195,174 @@
         <v>0.1018</v>
       </c>
       <c r="M24">
-        <v>-2.92E-2</v>
+        <v>-0.0292</v>
       </c>
       <c r="N24">
-        <v>0.43440000000000001</v>
+        <v>0.4344</v>
       </c>
       <c r="O24">
-        <v>9.2100000000000001E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>50</v>
+        <v>0.0921</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>YDR451C</v>
+      </c>
+      <c r="B25" t="str">
+        <v>YHP1</v>
       </c>
       <c r="C25">
         <v>-1.0359</v>
       </c>
       <c r="D25">
-        <v>-0.20899999999999999</v>
+        <v>-0.209</v>
       </c>
       <c r="E25">
         <v>-0.6754</v>
       </c>
       <c r="F25">
-        <v>-1.7565999999999999</v>
+        <v>-1.7566</v>
       </c>
       <c r="G25">
-        <v>-0.30480000000000002</v>
+        <v>-0.3048</v>
       </c>
       <c r="H25">
-        <v>1.1516999999999999</v>
+        <v>1.1517</v>
       </c>
       <c r="I25">
-        <v>0.86260000000000003</v>
+        <v>0.8626</v>
       </c>
       <c r="J25">
-        <v>-0.34100000000000003</v>
+        <v>-0.341</v>
       </c>
       <c r="K25">
         <v>-1.8669</v>
       </c>
       <c r="L25">
-        <v>0.64649999999999996</v>
+        <v>0.6465</v>
       </c>
       <c r="M25">
-        <v>0.57950000000000002</v>
+        <v>0.5795</v>
       </c>
       <c r="N25">
         <v>0.1827</v>
       </c>
       <c r="O25">
-        <v>-0.69259999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
-      <c r="A26" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>51</v>
+        <v>-0.6926</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>YLR278C</v>
+      </c>
+      <c r="B26" t="str">
+        <v>YLR278C</v>
       </c>
       <c r="C26">
-        <v>-1.1399999999999999</v>
+        <v>-1.14</v>
       </c>
       <c r="D26">
-        <v>-0.97789999999999999</v>
+        <v>-0.9779</v>
       </c>
       <c r="E26">
-        <v>-0.69130000000000003</v>
+        <v>-0.6913</v>
       </c>
       <c r="F26">
-        <v>-1.7069000000000001</v>
+        <v>-1.7069</v>
       </c>
       <c r="G26">
-        <v>-2.1208999999999998</v>
+        <v>-2.1209</v>
       </c>
       <c r="H26">
-        <v>0.42630000000000001</v>
+        <v>0.4263</v>
       </c>
       <c r="I26">
         <v>-1.0689</v>
       </c>
       <c r="J26">
-        <v>9.1000000000000004E-3</v>
+        <v>0.0091</v>
       </c>
       <c r="K26">
         <v>-1.5022</v>
       </c>
       <c r="L26">
-        <v>-1.7794000000000001</v>
+        <v>-1.7794</v>
       </c>
       <c r="M26">
-        <v>-1.3169999999999999</v>
+        <v>-1.317</v>
       </c>
       <c r="N26">
-        <v>-0.51490000000000002</v>
+        <v>-0.5149</v>
       </c>
       <c r="O26">
-        <v>-0.32600000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
-      <c r="A27" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>53</v>
+        <v>-0.326</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>YML027W</v>
+      </c>
+      <c r="B27" t="str">
+        <v>YOX1</v>
       </c>
       <c r="C27">
-        <v>-0.20810000000000001</v>
+        <v>-0.2081</v>
       </c>
       <c r="D27">
-        <v>-1.0712999999999999</v>
+        <v>-1.0713</v>
       </c>
       <c r="E27">
-        <v>-0.63990000000000002</v>
+        <v>-0.6399</v>
       </c>
       <c r="F27">
         <v>-2.238</v>
       </c>
       <c r="G27">
-        <v>-8.5800000000000001E-2</v>
+        <v>-0.0858</v>
       </c>
       <c r="H27">
-        <v>-1.6870000000000001</v>
+        <v>-1.687</v>
       </c>
       <c r="I27">
         <v>-0.108</v>
       </c>
       <c r="J27">
-        <v>-0.15090000000000001</v>
+        <v>-0.1509</v>
       </c>
       <c r="K27">
-        <v>-0.94789999999999996</v>
+        <v>-0.9479</v>
       </c>
       <c r="L27">
-        <v>-0.57789999999999997</v>
+        <v>-0.5779</v>
       </c>
       <c r="M27">
-        <v>0.13800000000000001</v>
+        <v>0.138</v>
       </c>
       <c r="N27">
         <v>-0.6946</v>
       </c>
       <c r="O27">
-        <v>-0.52159999999999995</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
-      <c r="A28" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>55</v>
+        <v>-0.5216</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>YJL056C</v>
+      </c>
+      <c r="B28" t="str">
+        <v>ZAP1</v>
       </c>
       <c r="C28">
-        <v>0.70030000000000003</v>
+        <v>0.7003</v>
       </c>
       <c r="D28">
-        <v>0.71640000000000004</v>
+        <v>0.7164</v>
       </c>
       <c r="E28">
-        <v>0.37040000000000001</v>
+        <v>0.3704</v>
       </c>
       <c r="F28">
-        <v>-0.38519999999999999</v>
+        <v>-0.3852</v>
       </c>
       <c r="G28">
         <v>1.5464</v>
@@ -3458,52 +2371,45 @@
         <v>1.7925</v>
       </c>
       <c r="I28">
-        <v>0.63900000000000001</v>
+        <v>0.639</v>
       </c>
       <c r="J28">
-        <v>-0.26450000000000001</v>
+        <v>-0.2645</v>
       </c>
       <c r="K28">
-        <v>-0.40760000000000002</v>
+        <v>-0.4076</v>
       </c>
       <c r="L28">
-        <v>2.9325000000000001</v>
+        <v>2.9325</v>
       </c>
       <c r="M28">
-        <v>3.3399000000000001</v>
+        <v>3.3399</v>
       </c>
       <c r="N28">
-        <v>1.5615000000000001</v>
+        <v>1.5615</v>
       </c>
       <c r="O28">
-        <v>1.0920000000000001</v>
+        <v>1.092</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:O28"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr enableFormatConditionsCalculation="0">
-    <tabColor rgb="FFFFFFFF"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="13" x14ac:dyDescent="0"/>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>SystematicName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>StandardName</v>
       </c>
       <c r="C1">
         <v>15</v>
@@ -3542,24 +2448,24 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>YLR131C</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ACE2</v>
       </c>
       <c r="C2">
         <v>-0.2429</v>
       </c>
       <c r="D2">
-        <v>-0.31680000000000003</v>
+        <v>-0.3168</v>
       </c>
       <c r="E2">
-        <v>-0.17249999999999999</v>
+        <v>-0.1725</v>
       </c>
       <c r="F2">
-        <v>-0.68340000000000001</v>
+        <v>-0.6834</v>
       </c>
       <c r="G2">
         <v>-0.2404</v>
@@ -3568,148 +2474,148 @@
         <v>0.1552</v>
       </c>
       <c r="I2">
-        <v>-0.43430000000000002</v>
+        <v>-0.4343</v>
       </c>
       <c r="J2">
-        <v>-1.3923000000000001</v>
+        <v>-1.3923</v>
       </c>
       <c r="K2">
-        <v>0.61670000000000003</v>
+        <v>0.6167</v>
       </c>
       <c r="L2">
-        <v>0.16059999999999999</v>
+        <v>0.1606</v>
       </c>
       <c r="M2">
-        <v>-0.31380000000000002</v>
+        <v>-0.3138</v>
       </c>
       <c r="N2">
-        <v>-0.37590000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>-0.3759</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>YIL130W</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ASG1</v>
       </c>
       <c r="C3">
-        <v>0.17430000000000001</v>
+        <v>0.1743</v>
       </c>
       <c r="D3">
-        <v>0.93320000000000003</v>
+        <v>0.9332</v>
       </c>
       <c r="E3">
-        <v>0.24229999999999999</v>
+        <v>0.2423</v>
       </c>
       <c r="F3">
-        <v>-0.48060000000000003</v>
+        <v>-0.4806</v>
       </c>
       <c r="G3">
-        <v>0.31890000000000002</v>
+        <v>0.3189</v>
       </c>
       <c r="H3">
-        <v>0.86299999999999999</v>
+        <v>0.863</v>
       </c>
       <c r="I3">
-        <v>-0.39850000000000002</v>
+        <v>-0.3985</v>
       </c>
       <c r="J3">
-        <v>-0.54800000000000004</v>
+        <v>-0.548</v>
       </c>
       <c r="K3">
         <v>-0.874</v>
       </c>
       <c r="L3">
-        <v>1.1476999999999999</v>
+        <v>1.1477</v>
       </c>
       <c r="M3">
-        <v>-0.17169999999999999</v>
+        <v>-0.1717</v>
       </c>
       <c r="N3">
         <v>-1.1032</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>YJR060W</v>
+      </c>
+      <c r="B4" t="str">
+        <v>CBF1</v>
       </c>
       <c r="C4">
-        <v>1.0174000000000001</v>
+        <v>1.0174</v>
       </c>
       <c r="D4">
-        <v>-0.51859999999999995</v>
+        <v>-0.5186</v>
       </c>
       <c r="E4">
-        <v>-0.61570000000000003</v>
+        <v>-0.6157</v>
       </c>
       <c r="F4">
         <v>-1.3868</v>
       </c>
       <c r="G4">
-        <v>-1.1059000000000001</v>
+        <v>-1.1059</v>
       </c>
       <c r="H4">
-        <v>-0.29570000000000002</v>
+        <v>-0.2957</v>
       </c>
       <c r="I4">
-        <v>-1.2188000000000001</v>
+        <v>-1.2188</v>
       </c>
       <c r="J4">
         <v>-1.2677</v>
       </c>
       <c r="K4">
-        <v>0.19159999999999999</v>
+        <v>0.1916</v>
       </c>
       <c r="L4">
-        <v>-0.23549999999999999</v>
+        <v>-0.2355</v>
       </c>
       <c r="M4">
-        <v>-0.61060000000000003</v>
+        <v>-0.6106</v>
       </c>
       <c r="N4">
         <v>-1.1714</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>YOR028C</v>
+      </c>
+      <c r="B5" t="str">
+        <v>CIN5</v>
       </c>
       <c r="C5">
-        <v>-0.78769999999999996</v>
+        <v>-0.7877</v>
       </c>
       <c r="D5">
-        <v>0.81679999999999997</v>
+        <v>0.8168</v>
       </c>
       <c r="E5">
-        <v>-0.54779999999999995</v>
+        <v>-0.5478</v>
       </c>
       <c r="F5">
-        <v>-0.14380000000000001</v>
+        <v>-0.1438</v>
       </c>
       <c r="G5">
-        <v>-0.60409999999999997</v>
+        <v>-0.6041</v>
       </c>
       <c r="H5">
-        <v>0.38090000000000002</v>
+        <v>0.3809</v>
       </c>
       <c r="I5">
         <v>-0.1138</v>
       </c>
       <c r="J5">
-        <v>0.69510000000000005</v>
+        <v>0.6951</v>
       </c>
       <c r="K5">
-        <v>-0.34670000000000001</v>
+        <v>-0.3467</v>
       </c>
       <c r="L5">
-        <v>-0.36940000000000001</v>
+        <v>-0.3694</v>
       </c>
       <c r="M5">
         <v>0.1072</v>
@@ -3718,112 +2624,112 @@
         <v>0.5786</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>YBR112C</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CYC8</v>
       </c>
       <c r="C6">
         <v>-1.0263</v>
       </c>
       <c r="D6">
-        <v>-8.1799999999999998E-2</v>
+        <v>-0.0818</v>
       </c>
       <c r="E6">
-        <v>-0.82789999999999997</v>
+        <v>-0.8279</v>
       </c>
       <c r="F6">
         <v>-1.153</v>
       </c>
       <c r="G6">
-        <v>-0.68220000000000003</v>
+        <v>-0.6822</v>
       </c>
       <c r="H6">
-        <v>0.94710000000000005</v>
+        <v>0.9471</v>
       </c>
       <c r="I6">
         <v>-0.5554</v>
       </c>
       <c r="J6">
-        <v>-0.26629999999999998</v>
+        <v>-0.2663</v>
       </c>
       <c r="K6">
-        <v>-0.55640000000000001</v>
+        <v>-0.5564</v>
       </c>
       <c r="L6">
-        <v>0.10349999999999999</v>
+        <v>0.1035</v>
       </c>
       <c r="M6">
         <v>-1.0448</v>
       </c>
       <c r="N6">
-        <v>-0.57930000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>14</v>
+        <v>-0.5793</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>YNL068C</v>
+      </c>
+      <c r="B7" t="str">
+        <v>FKH2</v>
       </c>
       <c r="C7">
-        <v>3.5999999999999999E-3</v>
+        <v>0.0036</v>
       </c>
       <c r="D7">
-        <v>-0.89880000000000004</v>
+        <v>-0.8988</v>
       </c>
       <c r="E7">
-        <v>-1.1664000000000001</v>
+        <v>-1.1664</v>
       </c>
       <c r="F7">
-        <v>-0.79949999999999999</v>
+        <v>-0.7995</v>
       </c>
       <c r="G7">
-        <v>-0.22059999999999999</v>
+        <v>-0.2206</v>
       </c>
       <c r="H7">
         <v>-0.5292</v>
       </c>
       <c r="I7">
-        <v>3.04E-2</v>
+        <v>0.0304</v>
       </c>
       <c r="J7">
-        <v>-1.6214999999999999</v>
+        <v>-1.6215</v>
       </c>
       <c r="K7">
         <v>0.1111</v>
       </c>
       <c r="L7">
-        <v>-0.15210000000000001</v>
+        <v>-0.1521</v>
       </c>
       <c r="M7">
-        <v>-0.43159999999999998</v>
+        <v>-0.4316</v>
       </c>
       <c r="N7">
-        <v>-1.0054000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>-1.0054</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>YLR013W</v>
+      </c>
+      <c r="B8" t="str">
+        <v>GAT3</v>
       </c>
       <c r="C8">
-        <v>-0.37619999999999998</v>
+        <v>-0.3762</v>
       </c>
       <c r="D8">
-        <v>0.43859999999999999</v>
+        <v>0.4386</v>
       </c>
       <c r="E8">
-        <v>1.4301999999999999</v>
+        <v>1.4302</v>
       </c>
       <c r="F8">
-        <v>0.90720000000000001</v>
+        <v>0.9072</v>
       </c>
       <c r="G8">
         <v>-0.1012</v>
@@ -3832,230 +2738,230 @@
         <v>0.6431</v>
       </c>
       <c r="I8">
-        <v>0.34689999999999999</v>
+        <v>0.3469</v>
       </c>
       <c r="J8">
         <v>0.628</v>
       </c>
       <c r="K8">
-        <v>-0.55900000000000005</v>
+        <v>-0.559</v>
       </c>
       <c r="L8">
-        <v>0.92589999999999995</v>
+        <v>0.9259</v>
       </c>
       <c r="M8">
-        <v>0.74680000000000002</v>
+        <v>0.7468</v>
       </c>
       <c r="N8">
-        <v>0.67679999999999996</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>0.6768</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>YNL199C</v>
+      </c>
+      <c r="B9" t="str">
+        <v>GCR2</v>
       </c>
       <c r="C9">
-        <v>-0.34279999999999999</v>
+        <v>-0.3428</v>
       </c>
       <c r="D9">
-        <v>1.7149000000000001</v>
+        <v>1.7149</v>
       </c>
       <c r="E9">
-        <v>-0.77190000000000003</v>
+        <v>-0.7719</v>
       </c>
       <c r="F9">
         <v>0.54</v>
       </c>
       <c r="G9">
-        <v>-0.72819999999999996</v>
+        <v>-0.7282</v>
       </c>
       <c r="H9">
         <v>-1.1069</v>
       </c>
       <c r="I9">
-        <v>0.50029999999999997</v>
+        <v>0.5003</v>
       </c>
       <c r="J9">
         <v>-0.3009</v>
       </c>
       <c r="K9">
-        <v>-0.24740000000000001</v>
+        <v>-0.2474</v>
       </c>
       <c r="L9">
         <v>-0.9355</v>
       </c>
       <c r="M9">
-        <v>-1.3009999999999999</v>
+        <v>-1.301</v>
       </c>
       <c r="N9">
-        <v>0.16650000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>20</v>
+        <v>0.1665</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>YER040W</v>
+      </c>
+      <c r="B10" t="str">
+        <v>GLN3</v>
       </c>
       <c r="C10">
         <v>1.0139</v>
       </c>
       <c r="D10">
-        <v>-0.41510000000000002</v>
+        <v>-0.4151</v>
       </c>
       <c r="E10">
-        <v>0.30530000000000002</v>
+        <v>0.3053</v>
       </c>
       <c r="F10">
-        <v>-0.15720000000000001</v>
+        <v>-0.1572</v>
       </c>
       <c r="G10">
         <v>0.5706</v>
       </c>
       <c r="H10">
-        <v>4.1200000000000001E-2</v>
+        <v>0.0412</v>
       </c>
       <c r="I10">
-        <v>0.48649999999999999</v>
+        <v>0.4865</v>
       </c>
       <c r="J10">
-        <v>0.41089999999999999</v>
+        <v>0.4109</v>
       </c>
       <c r="K10">
         <v>1.1854</v>
       </c>
       <c r="L10">
-        <v>5.0999999999999997E-2</v>
+        <v>0.051</v>
       </c>
       <c r="M10">
-        <v>1.0774999999999999</v>
+        <v>1.0775</v>
       </c>
       <c r="N10">
-        <v>0.50749999999999995</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>22</v>
+        <v>0.5075</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>YDR174W</v>
+      </c>
+      <c r="B11" t="str">
+        <v>HMO1</v>
       </c>
       <c r="C11">
         <v>-0.9093</v>
       </c>
       <c r="D11">
-        <v>1.4783999999999999</v>
+        <v>1.4784</v>
       </c>
       <c r="E11">
-        <v>0.39100000000000001</v>
+        <v>0.391</v>
       </c>
       <c r="F11">
-        <v>-6.5299999999999997E-2</v>
+        <v>-0.0653</v>
       </c>
       <c r="G11">
         <v>1.4701</v>
       </c>
       <c r="H11">
-        <v>1.1561999999999999</v>
+        <v>1.1562</v>
       </c>
       <c r="I11">
-        <v>0.34470000000000001</v>
+        <v>0.3447</v>
       </c>
       <c r="J11">
-        <v>-0.29570000000000002</v>
+        <v>-0.2957</v>
       </c>
       <c r="K11">
         <v>1.6653</v>
       </c>
       <c r="L11">
-        <v>2.6200999999999999</v>
+        <v>2.6201</v>
       </c>
       <c r="M11">
-        <v>0.84889999999999999</v>
+        <v>0.8489</v>
       </c>
       <c r="N11">
-        <v>1.3543000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>24</v>
+        <v>1.3543</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>YMR043W</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MCM1</v>
       </c>
       <c r="C12">
-        <v>0.54790000000000005</v>
+        <v>0.5479</v>
       </c>
       <c r="D12">
-        <v>0.53349999999999997</v>
+        <v>0.5335</v>
       </c>
       <c r="E12">
         <v>1.4579</v>
       </c>
       <c r="F12">
-        <v>2.4489000000000001</v>
+        <v>2.4489</v>
       </c>
       <c r="G12">
-        <v>1.7445999999999999</v>
+        <v>1.7446</v>
       </c>
       <c r="H12">
-        <v>-0.94820000000000004</v>
+        <v>-0.9482</v>
       </c>
       <c r="I12">
-        <v>0.75290000000000001</v>
+        <v>0.7529</v>
       </c>
       <c r="J12">
         <v>-0.1072</v>
       </c>
       <c r="K12">
-        <v>0.54510000000000003</v>
+        <v>0.5451</v>
       </c>
       <c r="L12">
-        <v>2.4899999999999999E-2</v>
+        <v>0.0249</v>
       </c>
       <c r="M12">
-        <v>1.0818000000000001</v>
+        <v>1.0818</v>
       </c>
       <c r="N12">
-        <v>1.2991999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>26</v>
+        <v>1.2992</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>YGL209W</v>
+      </c>
+      <c r="B13" t="str">
+        <v>MIG2</v>
       </c>
       <c r="C13">
-        <v>5.2977999999999996</v>
+        <v>5.2978</v>
       </c>
       <c r="D13">
-        <v>0.16209999999999999</v>
+        <v>0.1621</v>
       </c>
       <c r="E13">
-        <v>6.3574000000000002</v>
+        <v>6.3574</v>
       </c>
       <c r="F13">
-        <v>2.0390000000000001</v>
+        <v>2.039</v>
       </c>
       <c r="G13">
-        <v>-0.80069999999999997</v>
+        <v>-0.8007</v>
       </c>
       <c r="H13">
-        <v>-0.16470000000000001</v>
+        <v>-0.1647</v>
       </c>
       <c r="I13">
-        <v>0.87150000000000005</v>
+        <v>0.8715</v>
       </c>
       <c r="J13">
-        <v>5.3803999999999998</v>
+        <v>5.3804</v>
       </c>
       <c r="K13">
         <v>-1.2335</v>
@@ -4064,36 +2970,36 @@
         <v>-2.1347</v>
       </c>
       <c r="M13">
-        <v>-1.4383999999999999</v>
+        <v>-1.4384</v>
       </c>
       <c r="N13">
-        <v>-2.9944999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>28</v>
+        <v>-2.9945</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>YMR037C</v>
+      </c>
+      <c r="B14" t="str">
+        <v>MSN2</v>
       </c>
       <c r="C14">
-        <v>-9.0499999999999997E-2</v>
+        <v>-0.0905</v>
       </c>
       <c r="D14">
-        <v>-0.66900000000000004</v>
+        <v>-0.669</v>
       </c>
       <c r="E14">
-        <v>0.27579999999999999</v>
+        <v>0.2758</v>
       </c>
       <c r="F14">
         <v>0.9214</v>
       </c>
       <c r="G14">
-        <v>-0.53159999999999996</v>
+        <v>-0.5316</v>
       </c>
       <c r="H14">
-        <v>5.4999999999999997E-3</v>
+        <v>0.0055</v>
       </c>
       <c r="I14">
         <v>-0.1022</v>
@@ -4102,42 +3008,42 @@
         <v>1.0521</v>
       </c>
       <c r="K14">
-        <v>-0.11409999999999999</v>
+        <v>-0.1141</v>
       </c>
       <c r="L14">
-        <v>2.4E-2</v>
+        <v>0.024</v>
       </c>
       <c r="M14">
         <v>0.4325</v>
       </c>
       <c r="N14">
-        <v>5.1700000000000003E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>30</v>
+        <v>0.0517</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>YKL062W</v>
+      </c>
+      <c r="B15" t="str">
+        <v>MSN4</v>
       </c>
       <c r="C15">
-        <v>0.59950000000000003</v>
+        <v>0.5995</v>
       </c>
       <c r="D15">
         <v>1.5986</v>
       </c>
       <c r="E15">
-        <v>1.2472000000000001</v>
+        <v>1.2472</v>
       </c>
       <c r="F15">
-        <v>1.7146999999999999</v>
+        <v>1.7147</v>
       </c>
       <c r="G15">
-        <v>0.26640000000000003</v>
+        <v>0.2664</v>
       </c>
       <c r="H15">
-        <v>9.06E-2</v>
+        <v>0.0906</v>
       </c>
       <c r="I15">
         <v>1.9875</v>
@@ -4146,36 +3052,36 @@
         <v>1.0641</v>
       </c>
       <c r="K15">
-        <v>0.91969999999999996</v>
+        <v>0.9197</v>
       </c>
       <c r="L15">
         <v>0.2109</v>
       </c>
       <c r="M15">
-        <v>2.6684000000000001</v>
+        <v>2.6684</v>
       </c>
       <c r="N15">
         <v>1.57</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>32</v>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>YGL013C</v>
+      </c>
+      <c r="B16" t="str">
+        <v>PDR1</v>
       </c>
       <c r="C16">
-        <v>-0.64080000000000004</v>
+        <v>-0.6408</v>
       </c>
       <c r="D16">
-        <v>0.34010000000000001</v>
+        <v>0.3401</v>
       </c>
       <c r="E16">
-        <v>1.0188999999999999</v>
+        <v>1.0189</v>
       </c>
       <c r="F16">
-        <v>-0.63529999999999998</v>
+        <v>-0.6353</v>
       </c>
       <c r="G16">
         <v>-0.3957</v>
@@ -4184,39 +3090,39 @@
         <v>-1.1955</v>
       </c>
       <c r="I16">
-        <v>0.58589999999999998</v>
+        <v>0.5859</v>
       </c>
       <c r="J16">
-        <v>-0.95879999999999999</v>
+        <v>-0.9588</v>
       </c>
       <c r="K16">
-        <v>0.27489999999999998</v>
+        <v>0.2749</v>
       </c>
       <c r="L16">
-        <v>-0.60060000000000002</v>
+        <v>-0.6006</v>
       </c>
       <c r="M16">
-        <v>0.52610000000000001</v>
+        <v>0.5261</v>
       </c>
       <c r="N16">
-        <v>0.25890000000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>34</v>
+        <v>0.2589</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>YNR052C</v>
+      </c>
+      <c r="B17" t="str">
+        <v>POP2</v>
       </c>
       <c r="C17">
-        <v>0.62239999999999995</v>
+        <v>0.6224</v>
       </c>
       <c r="D17">
         <v>1.07</v>
       </c>
       <c r="E17">
-        <v>1.6789000000000001</v>
+        <v>1.6789</v>
       </c>
       <c r="F17">
         <v>1.3975</v>
@@ -4225,209 +3131,209 @@
         <v>1.5361</v>
       </c>
       <c r="H17">
-        <v>6.4399999999999999E-2</v>
+        <v>0.0644</v>
       </c>
       <c r="I17">
-        <v>0.47570000000000001</v>
+        <v>0.4757</v>
       </c>
       <c r="J17">
-        <v>0.14330000000000001</v>
+        <v>0.1433</v>
       </c>
       <c r="K17">
-        <v>0.88070000000000004</v>
+        <v>0.8807</v>
       </c>
       <c r="L17">
-        <v>0.37609999999999999</v>
+        <v>0.3761</v>
       </c>
       <c r="M17">
-        <v>-0.17349999999999999</v>
+        <v>-0.1735</v>
       </c>
       <c r="N17">
-        <v>1.1708000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>36</v>
+        <v>1.1708</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>YBR275C</v>
+      </c>
+      <c r="B18" t="str">
+        <v>RIF1</v>
       </c>
       <c r="C18">
-        <v>0.73570000000000002</v>
+        <v>0.7357</v>
       </c>
       <c r="D18">
-        <v>0.23069999999999999</v>
+        <v>0.2307</v>
       </c>
       <c r="E18">
-        <v>0.32669999999999999</v>
+        <v>0.3267</v>
       </c>
       <c r="F18">
-        <v>0.32579999999999998</v>
+        <v>0.3258</v>
       </c>
       <c r="G18">
-        <v>0.66739999999999999</v>
+        <v>0.6674</v>
       </c>
       <c r="H18">
-        <v>4.1799999999999997E-2</v>
+        <v>0.0418</v>
       </c>
       <c r="I18">
-        <v>0.35270000000000001</v>
+        <v>0.3527</v>
       </c>
       <c r="J18">
-        <v>0.91220000000000001</v>
+        <v>0.9122</v>
       </c>
       <c r="K18">
-        <v>0.22220000000000001</v>
+        <v>0.2222</v>
       </c>
       <c r="L18">
-        <v>0.49130000000000001</v>
+        <v>0.4913</v>
       </c>
       <c r="M18">
-        <v>-9.74E-2</v>
+        <v>-0.0974</v>
       </c>
       <c r="N18">
         <v>0.5484</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>38</v>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>YPL089C</v>
+      </c>
+      <c r="B19" t="str">
+        <v>RLM1</v>
       </c>
       <c r="C19">
-        <v>-0.36840000000000001</v>
+        <v>-0.3684</v>
       </c>
       <c r="D19">
         <v>2.0625</v>
       </c>
       <c r="E19">
-        <v>0.27110000000000001</v>
+        <v>0.2711</v>
       </c>
       <c r="F19">
-        <v>7.9000000000000008E-3</v>
+        <v>0.0079</v>
       </c>
       <c r="G19">
-        <v>-0.58579999999999999</v>
+        <v>-0.5858</v>
       </c>
       <c r="H19">
-        <v>0.30649999999999999</v>
+        <v>0.3065</v>
       </c>
       <c r="I19">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="J19">
-        <v>-0.15609999999999999</v>
+        <v>-0.1561</v>
       </c>
       <c r="K19">
-        <v>0.40860000000000002</v>
+        <v>0.4086</v>
       </c>
       <c r="L19">
-        <v>-0.18640000000000001</v>
+        <v>-0.1864</v>
       </c>
       <c r="M19">
-        <v>-0.20419999999999999</v>
+        <v>-0.2042</v>
       </c>
       <c r="N19">
-        <v>6.6E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>40</v>
+        <v>0.0066</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>YLR403W</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SFP1</v>
       </c>
       <c r="C20">
         <v>1.1814</v>
       </c>
       <c r="D20">
-        <v>0.57169999999999999</v>
+        <v>0.5717</v>
       </c>
       <c r="E20">
-        <v>1.1356999999999999</v>
+        <v>1.1357</v>
       </c>
       <c r="F20">
-        <v>0.63049999999999995</v>
+        <v>0.6305</v>
       </c>
       <c r="G20">
-        <v>0.50139999999999996</v>
+        <v>0.5014</v>
       </c>
       <c r="H20">
-        <v>-0.36620000000000003</v>
+        <v>-0.3662</v>
       </c>
       <c r="I20">
-        <v>1.6021000000000001</v>
+        <v>1.6021</v>
       </c>
       <c r="J20">
         <v>-0.1115</v>
       </c>
       <c r="K20">
-        <v>0.70550000000000002</v>
+        <v>0.7055</v>
       </c>
       <c r="L20">
-        <v>0.67849999999999999</v>
+        <v>0.6785</v>
       </c>
       <c r="M20">
-        <v>0.91169999999999995</v>
+        <v>0.9117</v>
       </c>
       <c r="N20">
         <v>0.2828</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>42</v>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>YOR290C</v>
+      </c>
+      <c r="B21" t="str">
+        <v>SNF2</v>
       </c>
       <c r="C21">
-        <v>-0.60389999999999999</v>
+        <v>-0.6039</v>
       </c>
       <c r="D21">
-        <v>0.36680000000000001</v>
+        <v>0.3668</v>
       </c>
       <c r="E21">
-        <v>0.17480000000000001</v>
+        <v>0.1748</v>
       </c>
       <c r="F21">
         <v>-1.1814</v>
       </c>
       <c r="G21">
-        <v>-0.16189999999999999</v>
+        <v>-0.1619</v>
       </c>
       <c r="H21">
-        <v>1.0760000000000001</v>
+        <v>1.076</v>
       </c>
       <c r="I21">
         <v>0.1462</v>
       </c>
       <c r="J21">
-        <v>-1.6587000000000001</v>
+        <v>-1.6587</v>
       </c>
       <c r="K21">
-        <v>-0.13039999999999999</v>
+        <v>-0.1304</v>
       </c>
       <c r="L21">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="M21">
-        <v>-0.45219999999999999</v>
+        <v>-0.4522</v>
       </c>
       <c r="N21">
-        <v>-0.75090000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>44</v>
+        <v>-0.7509</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>YHL025W</v>
+      </c>
+      <c r="B22" t="str">
+        <v>SNF6</v>
       </c>
       <c r="C22">
         <v>-0.1666</v>
@@ -4436,28 +3342,28 @@
         <v>-1.0502</v>
       </c>
       <c r="E22">
-        <v>7.6700000000000004E-2</v>
+        <v>0.0767</v>
       </c>
       <c r="F22">
-        <v>-0.13389999999999999</v>
+        <v>-0.1339</v>
       </c>
       <c r="G22">
-        <v>1.0761000000000001</v>
+        <v>1.0761</v>
       </c>
       <c r="H22">
         <v>-1.5284</v>
       </c>
       <c r="I22">
-        <v>-0.29149999999999998</v>
+        <v>-0.2915</v>
       </c>
       <c r="J22">
-        <v>3.1199999999999999E-2</v>
+        <v>0.0312</v>
       </c>
       <c r="K22">
-        <v>7.4499999999999997E-2</v>
+        <v>0.0745</v>
       </c>
       <c r="L22">
-        <v>-0.35360000000000003</v>
+        <v>-0.3536</v>
       </c>
       <c r="M22">
         <v>-0.2702</v>
@@ -4466,42 +3372,42 @@
         <v>0.2293</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>46</v>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>YHR178W</v>
+      </c>
+      <c r="B23" t="str">
+        <v>STB5</v>
       </c>
       <c r="C23">
-        <v>1.2875000000000001</v>
+        <v>1.2875</v>
       </c>
       <c r="D23">
         <v>1.2539</v>
       </c>
       <c r="E23">
-        <v>0.86890000000000001</v>
+        <v>0.8689</v>
       </c>
       <c r="F23">
-        <v>0.79910000000000003</v>
+        <v>0.7991</v>
       </c>
       <c r="G23">
-        <v>-1.8375999999999999</v>
+        <v>-1.8376</v>
       </c>
       <c r="H23">
         <v>-0.437</v>
       </c>
       <c r="I23">
-        <v>0.54039999999999999</v>
+        <v>0.5404</v>
       </c>
       <c r="J23">
-        <v>1.1825000000000001</v>
+        <v>1.1825</v>
       </c>
       <c r="K23">
         <v>0.5595</v>
       </c>
       <c r="L23">
-        <v>0.28320000000000001</v>
+        <v>0.2832</v>
       </c>
       <c r="M23">
         <v>1.55</v>
@@ -4510,12 +3416,12 @@
         <v>1.0446</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>48</v>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>YDR146C</v>
+      </c>
+      <c r="B24" t="str">
+        <v>SWI5</v>
       </c>
       <c r="C24">
         <v>-0.127</v>
@@ -4527,157 +3433,157 @@
         <v>-0.3044</v>
       </c>
       <c r="F24">
-        <v>-1.29E-2</v>
+        <v>-0.0129</v>
       </c>
       <c r="G24">
-        <v>0.85540000000000005</v>
+        <v>0.8554</v>
       </c>
       <c r="H24">
-        <v>-0.40379999999999999</v>
+        <v>-0.4038</v>
       </c>
       <c r="I24">
-        <v>0.18959999999999999</v>
+        <v>0.1896</v>
       </c>
       <c r="J24">
-        <v>-0.70350000000000001</v>
+        <v>-0.7035</v>
       </c>
       <c r="K24">
-        <v>8.5900000000000004E-2</v>
+        <v>0.0859</v>
       </c>
       <c r="L24">
-        <v>-0.41649999999999998</v>
+        <v>-0.4165</v>
       </c>
       <c r="M24">
-        <v>0.82730000000000004</v>
+        <v>0.8273</v>
       </c>
       <c r="N24">
-        <v>0.21529999999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>50</v>
+        <v>0.2153</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>YDR451C</v>
+      </c>
+      <c r="B25" t="str">
+        <v>YHP1</v>
       </c>
       <c r="C25">
-        <v>-1.2587999999999999</v>
+        <v>-1.2588</v>
       </c>
       <c r="D25">
-        <v>0.38869999999999999</v>
+        <v>0.3887</v>
       </c>
       <c r="E25">
-        <v>-0.68240000000000001</v>
+        <v>-0.6824</v>
       </c>
       <c r="F25">
-        <v>0.29709999999999998</v>
+        <v>0.2971</v>
       </c>
       <c r="G25">
-        <v>-1.2231000000000001</v>
+        <v>-1.2231</v>
       </c>
       <c r="H25">
-        <v>-0.80200000000000005</v>
+        <v>-0.802</v>
       </c>
       <c r="I25">
-        <v>0.89190000000000003</v>
+        <v>0.8919</v>
       </c>
       <c r="J25">
-        <v>-0.73270000000000002</v>
+        <v>-0.7327</v>
       </c>
       <c r="K25">
-        <v>1.0840000000000001</v>
+        <v>1.084</v>
       </c>
       <c r="L25">
-        <v>-5.0700000000000002E-2</v>
+        <v>-0.0507</v>
       </c>
       <c r="M25">
-        <v>-0.80489999999999995</v>
+        <v>-0.8049</v>
       </c>
       <c r="N25">
-        <v>0.51659999999999995</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>51</v>
+        <v>0.5166</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>YLR278C</v>
+      </c>
+      <c r="B26" t="str">
+        <v>YLR278C</v>
       </c>
       <c r="C26">
         <v>-0.8901</v>
       </c>
       <c r="D26">
-        <v>1.1698999999999999</v>
+        <v>1.1699</v>
       </c>
       <c r="E26">
-        <v>-0.75319999999999998</v>
+        <v>-0.7532</v>
       </c>
       <c r="F26">
-        <v>-1.2091000000000001</v>
+        <v>-1.2091</v>
       </c>
       <c r="G26">
-        <v>0.11409999999999999</v>
+        <v>0.1141</v>
       </c>
       <c r="H26">
-        <v>2.07E-2</v>
+        <v>0.0207</v>
       </c>
       <c r="I26">
-        <v>-1.0032000000000001</v>
+        <v>-1.0032</v>
       </c>
       <c r="J26">
-        <v>-1.4732000000000001</v>
+        <v>-1.4732</v>
       </c>
       <c r="K26">
-        <v>0.23949999999999999</v>
+        <v>0.2395</v>
       </c>
       <c r="L26">
-        <v>-0.33839999999999998</v>
+        <v>-0.3384</v>
       </c>
       <c r="M26">
-        <v>-1.0553999999999999</v>
+        <v>-1.0554</v>
       </c>
       <c r="N26">
-        <v>-1.1184000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>53</v>
+        <v>-1.1184</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>YML027W</v>
+      </c>
+      <c r="B27" t="str">
+        <v>YOX1</v>
       </c>
       <c r="C27">
-        <v>-1.4866999999999999</v>
+        <v>-1.4867</v>
       </c>
       <c r="D27">
         <v>-1.0888</v>
       </c>
       <c r="E27">
-        <v>-1.6603000000000001</v>
+        <v>-1.6603</v>
       </c>
       <c r="F27">
-        <v>-0.29509999999999997</v>
+        <v>-0.2951</v>
       </c>
       <c r="G27">
-        <v>-6.4500000000000002E-2</v>
+        <v>-0.0645</v>
       </c>
       <c r="H27">
-        <v>-0.72750000000000004</v>
+        <v>-0.7275</v>
       </c>
       <c r="I27">
-        <v>-0.10979999999999999</v>
+        <v>-0.1098</v>
       </c>
       <c r="J27">
-        <v>-2.7490999999999999</v>
+        <v>-2.7491</v>
       </c>
       <c r="K27">
-        <v>0.77059999999999995</v>
+        <v>0.7706</v>
       </c>
       <c r="L27">
-        <v>0.53169999999999995</v>
+        <v>0.5317</v>
       </c>
       <c r="M27">
         <v>-1.4033</v>
@@ -4686,18 +3592,18 @@
         <v>0.3135</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
-      <c r="A28" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>55</v>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>YJL056C</v>
+      </c>
+      <c r="B28" t="str">
+        <v>ZAP1</v>
       </c>
       <c r="C28">
-        <v>0.87970000000000004</v>
+        <v>0.8797</v>
       </c>
       <c r="D28">
-        <v>1.1924999999999999</v>
+        <v>1.1925</v>
       </c>
       <c r="E28">
         <v>1.0264</v>
@@ -4706,140 +3612,131 @@
         <v>0.4975</v>
       </c>
       <c r="G28">
-        <v>2.5400999999999998</v>
+        <v>2.5401</v>
       </c>
       <c r="H28">
         <v>0.1414</v>
       </c>
       <c r="I28">
-        <v>0.74429999999999996</v>
+        <v>0.7443</v>
       </c>
       <c r="J28">
-        <v>-0.84209999999999996</v>
+        <v>-0.8421</v>
       </c>
       <c r="K28">
-        <v>0.36020000000000002</v>
+        <v>0.3602</v>
       </c>
       <c r="L28">
-        <v>-9.6799999999999997E-2</v>
+        <v>-0.0968</v>
       </c>
       <c r="M28">
-        <v>1.1032999999999999</v>
+        <v>1.1033</v>
       </c>
       <c r="N28">
-        <v>-4.8800000000000003E-2</v>
+        <v>-0.0488</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:N28"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr enableFormatConditionsCalculation="0">
-    <tabColor rgb="FFFFFFFF"/>
-  </sheetPr>
-  <dimension ref="A1:AE28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="13" x14ac:dyDescent="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AB28"/>
   <sheetData>
-    <row r="1" spans="1:31">
-      <c r="A1" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P1" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S1" t="s">
-        <v>38</v>
-      </c>
-      <c r="T1" t="s">
-        <v>40</v>
-      </c>
-      <c r="U1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W1" t="s">
-        <v>46</v>
-      </c>
-      <c r="X1" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC1" s="3"/>
-      <c r="AD1" s="3"/>
-    </row>
-    <row r="2" spans="1:31">
-      <c r="A2" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>cols regulators/rows targets</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ACE2</v>
+      </c>
+      <c r="C1" t="str">
+        <v>ASG1</v>
+      </c>
+      <c r="D1" t="str">
+        <v>CBF1</v>
+      </c>
+      <c r="E1" t="str">
+        <v>CIN5</v>
+      </c>
+      <c r="F1" t="str">
+        <v>CYC8</v>
+      </c>
+      <c r="G1" t="str">
+        <v>FKH2</v>
+      </c>
+      <c r="H1" t="str">
+        <v>GAT3</v>
+      </c>
+      <c r="I1" t="str">
+        <v>GCR2</v>
+      </c>
+      <c r="J1" t="str">
+        <v>GLN3</v>
+      </c>
+      <c r="K1" t="str">
+        <v>HMO1</v>
+      </c>
+      <c r="L1" t="str">
+        <v>MCM1</v>
+      </c>
+      <c r="M1" t="str">
+        <v>MIG2</v>
+      </c>
+      <c r="N1" t="str">
+        <v>MSN2</v>
+      </c>
+      <c r="O1" t="str">
+        <v>MSN4</v>
+      </c>
+      <c r="P1" t="str">
+        <v>PDR1</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>POP2</v>
+      </c>
+      <c r="R1" t="str">
+        <v>RIF1</v>
+      </c>
+      <c r="S1" t="str">
+        <v>RLM1</v>
+      </c>
+      <c r="T1" t="str">
+        <v>SFP1</v>
+      </c>
+      <c r="U1" t="str">
+        <v>SNF2</v>
+      </c>
+      <c r="V1" t="str">
+        <v>SNF6</v>
+      </c>
+      <c r="W1" t="str">
+        <v>STB5</v>
+      </c>
+      <c r="X1" t="str">
+        <v>SWI5</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>YHP1</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>YLR278C</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>YOX1</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>ZAP1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ACE2</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -4922,13 +3819,10 @@
       <c r="AB2">
         <v>1</v>
       </c>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="3"/>
-    </row>
-    <row r="3" spans="1:31">
-      <c r="A3" t="s">
-        <v>6</v>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ASG1</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5011,13 +3905,10 @@
       <c r="AB3">
         <v>0</v>
       </c>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-    </row>
-    <row r="4" spans="1:31">
-      <c r="A4" t="s">
-        <v>8</v>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CBF1</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5100,13 +3991,10 @@
       <c r="AB4">
         <v>0</v>
       </c>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="3"/>
-    </row>
-    <row r="5" spans="1:31">
-      <c r="A5" t="s">
-        <v>10</v>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>CIN5</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5189,13 +4077,10 @@
       <c r="AB5">
         <v>0</v>
       </c>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3"/>
-    </row>
-    <row r="6" spans="1:31">
-      <c r="A6" t="s">
-        <v>12</v>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CYC8</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -5278,13 +4163,10 @@
       <c r="AB6">
         <v>0</v>
       </c>
-      <c r="AC6" s="3"/>
-      <c r="AD6" s="3"/>
-      <c r="AE6" s="3"/>
-    </row>
-    <row r="7" spans="1:31">
-      <c r="A7" t="s">
-        <v>14</v>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>FKH2</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -5367,13 +4249,10 @@
       <c r="AB7">
         <v>0</v>
       </c>
-      <c r="AC7" s="3"/>
-      <c r="AD7" s="3"/>
-      <c r="AE7" s="3"/>
-    </row>
-    <row r="8" spans="1:31">
-      <c r="A8" t="s">
-        <v>16</v>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>GAT3</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -5456,13 +4335,10 @@
       <c r="AB8">
         <v>0</v>
       </c>
-      <c r="AC8" s="3"/>
-      <c r="AD8" s="3"/>
-      <c r="AE8" s="3"/>
-    </row>
-    <row r="9" spans="1:31">
-      <c r="A9" t="s">
-        <v>18</v>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>GCR2</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -5545,13 +4421,10 @@
       <c r="AB9">
         <v>0</v>
       </c>
-      <c r="AC9" s="3"/>
-      <c r="AD9" s="3"/>
-      <c r="AE9" s="3"/>
-    </row>
-    <row r="10" spans="1:31">
-      <c r="A10" t="s">
-        <v>20</v>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>GLN3</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -5634,13 +4507,10 @@
       <c r="AB10">
         <v>0</v>
       </c>
-      <c r="AC10" s="3"/>
-      <c r="AD10" s="3"/>
-      <c r="AE10" s="3"/>
-    </row>
-    <row r="11" spans="1:31">
-      <c r="A11" t="s">
-        <v>22</v>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>HMO1</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -5723,13 +4593,10 @@
       <c r="AB11">
         <v>0</v>
       </c>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="3"/>
-      <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31">
-      <c r="A12" t="s">
-        <v>24</v>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>MCM1</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -5812,13 +4679,10 @@
       <c r="AB12">
         <v>0</v>
       </c>
-      <c r="AC12" s="3"/>
-      <c r="AD12" s="3"/>
-      <c r="AE12" s="3"/>
-    </row>
-    <row r="13" spans="1:31">
-      <c r="A13" t="s">
-        <v>26</v>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>MIG2</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -5901,13 +4765,10 @@
       <c r="AB13">
         <v>0</v>
       </c>
-      <c r="AC13" s="3"/>
-      <c r="AD13" s="3"/>
-      <c r="AE13" s="3"/>
-    </row>
-    <row r="14" spans="1:31">
-      <c r="A14" t="s">
-        <v>28</v>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>MSN2</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -5990,13 +4851,10 @@
       <c r="AB14">
         <v>0</v>
       </c>
-      <c r="AC14" s="3"/>
-      <c r="AD14" s="3"/>
-      <c r="AE14" s="3"/>
-    </row>
-    <row r="15" spans="1:31">
-      <c r="A15" t="s">
-        <v>30</v>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>MSN4</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -6079,13 +4937,10 @@
       <c r="AB15">
         <v>0</v>
       </c>
-      <c r="AC15" s="3"/>
-      <c r="AD15" s="3"/>
-      <c r="AE15" s="3"/>
-    </row>
-    <row r="16" spans="1:31">
-      <c r="A16" t="s">
-        <v>32</v>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>PDR1</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -6168,13 +5023,10 @@
       <c r="AB16">
         <v>0</v>
       </c>
-      <c r="AC16" s="3"/>
-      <c r="AD16" s="3"/>
-      <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="1:31">
-      <c r="A17" t="s">
-        <v>34</v>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>POP2</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -6257,13 +5109,10 @@
       <c r="AB17">
         <v>0</v>
       </c>
-      <c r="AC17" s="3"/>
-      <c r="AD17" s="3"/>
-      <c r="AE17" s="3"/>
-    </row>
-    <row r="18" spans="1:31">
-      <c r="A18" t="s">
-        <v>36</v>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>RIF1</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -6346,13 +5195,10 @@
       <c r="AB18">
         <v>0</v>
       </c>
-      <c r="AC18" s="3"/>
-      <c r="AD18" s="3"/>
-      <c r="AE18" s="3"/>
-    </row>
-    <row r="19" spans="1:31">
-      <c r="A19" t="s">
-        <v>38</v>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>RLM1</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -6435,13 +5281,10 @@
       <c r="AB19">
         <v>0</v>
       </c>
-      <c r="AC19" s="3"/>
-      <c r="AD19" s="3"/>
-      <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="1:31">
-      <c r="A20" t="s">
-        <v>40</v>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SFP1</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -6524,13 +5367,10 @@
       <c r="AB20">
         <v>0</v>
       </c>
-      <c r="AC20" s="3"/>
-      <c r="AD20" s="3"/>
-      <c r="AE20" s="3"/>
-    </row>
-    <row r="21" spans="1:31">
-      <c r="A21" t="s">
-        <v>42</v>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SNF2</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -6613,13 +5453,10 @@
       <c r="AB21">
         <v>0</v>
       </c>
-      <c r="AC21" s="3"/>
-      <c r="AD21" s="3"/>
-      <c r="AE21" s="3"/>
-    </row>
-    <row r="22" spans="1:31">
-      <c r="A22" t="s">
-        <v>44</v>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SNF6</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -6702,13 +5539,10 @@
       <c r="AB22">
         <v>0</v>
       </c>
-      <c r="AC22" s="3"/>
-      <c r="AD22" s="3"/>
-      <c r="AE22" s="3"/>
-    </row>
-    <row r="23" spans="1:31">
-      <c r="A23" t="s">
-        <v>46</v>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>STB5</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -6791,13 +5625,10 @@
       <c r="AB23">
         <v>0</v>
       </c>
-      <c r="AC23" s="3"/>
-      <c r="AD23" s="3"/>
-      <c r="AE23" s="3"/>
-    </row>
-    <row r="24" spans="1:31">
-      <c r="A24" t="s">
-        <v>48</v>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SWI5</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -6880,13 +5711,10 @@
       <c r="AB24">
         <v>0</v>
       </c>
-      <c r="AC24" s="3"/>
-      <c r="AD24" s="3"/>
-      <c r="AE24" s="3"/>
-    </row>
-    <row r="25" spans="1:31">
-      <c r="A25" t="s">
-        <v>50</v>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>YHP1</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -6969,13 +5797,10 @@
       <c r="AB25">
         <v>0</v>
       </c>
-      <c r="AC25" s="3"/>
-      <c r="AD25" s="3"/>
-      <c r="AE25" s="3"/>
-    </row>
-    <row r="26" spans="1:31">
-      <c r="A26" t="s">
-        <v>51</v>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>YLR278C</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -7058,13 +5883,10 @@
       <c r="AB26">
         <v>0</v>
       </c>
-      <c r="AC26" s="3"/>
-      <c r="AD26" s="3"/>
-      <c r="AE26" s="3"/>
-    </row>
-    <row r="27" spans="1:31">
-      <c r="A27" t="s">
-        <v>53</v>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>YOX1</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -7147,13 +5969,10 @@
       <c r="AB27">
         <v>0</v>
       </c>
-      <c r="AC27" s="3"/>
-      <c r="AD27" s="3"/>
-      <c r="AE27" s="3"/>
-    </row>
-    <row r="28" spans="1:31">
-      <c r="A28" t="s">
-        <v>55</v>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>ZAP1</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -7236,121 +6055,107 @@
       <c r="AB28">
         <v>0</v>
       </c>
-      <c r="AC28" s="3"/>
-      <c r="AD28" s="3"/>
-      <c r="AE28" s="3"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:AB28"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr enableFormatConditionsCalculation="0">
-    <tabColor rgb="FFFFFFFF"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AE28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="13" x14ac:dyDescent="0"/>
   <sheetData>
-    <row r="1" spans="1:31">
-      <c r="A1" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P1" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S1" t="s">
-        <v>38</v>
-      </c>
-      <c r="T1" t="s">
-        <v>40</v>
-      </c>
-      <c r="U1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W1" t="s">
-        <v>46</v>
-      </c>
-      <c r="X1" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC1" s="3"/>
-      <c r="AD1" s="3"/>
-      <c r="AE1" s="3"/>
-    </row>
-    <row r="2" spans="1:31">
-      <c r="A2" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>rows genes affected/cols genes controlling</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ACE2</v>
+      </c>
+      <c r="C1" t="str">
+        <v>ASG1</v>
+      </c>
+      <c r="D1" t="str">
+        <v>CBF1</v>
+      </c>
+      <c r="E1" t="str">
+        <v>CIN5</v>
+      </c>
+      <c r="F1" t="str">
+        <v>CYC8</v>
+      </c>
+      <c r="G1" t="str">
+        <v>FKH2</v>
+      </c>
+      <c r="H1" t="str">
+        <v>GAT3</v>
+      </c>
+      <c r="I1" t="str">
+        <v>GCR2</v>
+      </c>
+      <c r="J1" t="str">
+        <v>GLN3</v>
+      </c>
+      <c r="K1" t="str">
+        <v>HMO1</v>
+      </c>
+      <c r="L1" t="str">
+        <v>MCM1</v>
+      </c>
+      <c r="M1" t="str">
+        <v>MIG2</v>
+      </c>
+      <c r="N1" t="str">
+        <v>MSN2</v>
+      </c>
+      <c r="O1" t="str">
+        <v>MSN4</v>
+      </c>
+      <c r="P1" t="str">
+        <v>PDR1</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>POP2</v>
+      </c>
+      <c r="R1" t="str">
+        <v>RIF1</v>
+      </c>
+      <c r="S1" t="str">
+        <v>RLM1</v>
+      </c>
+      <c r="T1" t="str">
+        <v>SFP1</v>
+      </c>
+      <c r="U1" t="str">
+        <v>SNF2</v>
+      </c>
+      <c r="V1" t="str">
+        <v>SNF6</v>
+      </c>
+      <c r="W1" t="str">
+        <v>STB5</v>
+      </c>
+      <c r="X1" t="str">
+        <v>SWI5</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>YHP1</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>YLR278C</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>YOX1</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>ZAP1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ACE2</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -7433,13 +6238,10 @@
       <c r="AB2">
         <v>1</v>
       </c>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="3"/>
-    </row>
-    <row r="3" spans="1:31">
-      <c r="A3" t="s">
-        <v>6</v>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ASG1</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7522,13 +6324,10 @@
       <c r="AB3">
         <v>0</v>
       </c>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-    </row>
-    <row r="4" spans="1:31">
-      <c r="A4" t="s">
-        <v>8</v>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CBF1</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7611,13 +6410,10 @@
       <c r="AB4">
         <v>0</v>
       </c>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="3"/>
-    </row>
-    <row r="5" spans="1:31">
-      <c r="A5" t="s">
-        <v>10</v>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>CIN5</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7700,13 +6496,10 @@
       <c r="AB5">
         <v>0</v>
       </c>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3"/>
-    </row>
-    <row r="6" spans="1:31">
-      <c r="A6" t="s">
-        <v>12</v>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CYC8</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7789,13 +6582,10 @@
       <c r="AB6">
         <v>0</v>
       </c>
-      <c r="AC6" s="3"/>
-      <c r="AD6" s="3"/>
-      <c r="AE6" s="3"/>
-    </row>
-    <row r="7" spans="1:31">
-      <c r="A7" t="s">
-        <v>14</v>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>FKH2</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -7878,13 +6668,10 @@
       <c r="AB7">
         <v>0</v>
       </c>
-      <c r="AC7" s="3"/>
-      <c r="AD7" s="3"/>
-      <c r="AE7" s="3"/>
-    </row>
-    <row r="8" spans="1:31">
-      <c r="A8" t="s">
-        <v>16</v>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>GAT3</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -7967,13 +6754,10 @@
       <c r="AB8">
         <v>0</v>
       </c>
-      <c r="AC8" s="3"/>
-      <c r="AD8" s="3"/>
-      <c r="AE8" s="3"/>
-    </row>
-    <row r="9" spans="1:31">
-      <c r="A9" t="s">
-        <v>18</v>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>GCR2</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8056,13 +6840,10 @@
       <c r="AB9">
         <v>0</v>
       </c>
-      <c r="AC9" s="3"/>
-      <c r="AD9" s="3"/>
-      <c r="AE9" s="3"/>
-    </row>
-    <row r="10" spans="1:31">
-      <c r="A10" t="s">
-        <v>20</v>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>GLN3</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -8145,13 +6926,10 @@
       <c r="AB10">
         <v>0</v>
       </c>
-      <c r="AC10" s="3"/>
-      <c r="AD10" s="3"/>
-      <c r="AE10" s="3"/>
-    </row>
-    <row r="11" spans="1:31">
-      <c r="A11" t="s">
-        <v>22</v>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>HMO1</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -8234,13 +7012,10 @@
       <c r="AB11">
         <v>0</v>
       </c>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="3"/>
-      <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31">
-      <c r="A12" t="s">
-        <v>24</v>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>MCM1</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -8323,13 +7098,10 @@
       <c r="AB12">
         <v>0</v>
       </c>
-      <c r="AC12" s="3"/>
-      <c r="AD12" s="3"/>
-      <c r="AE12" s="3"/>
-    </row>
-    <row r="13" spans="1:31">
-      <c r="A13" t="s">
-        <v>26</v>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>MIG2</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -8412,13 +7184,10 @@
       <c r="AB13">
         <v>0</v>
       </c>
-      <c r="AC13" s="3"/>
-      <c r="AD13" s="3"/>
-      <c r="AE13" s="3"/>
-    </row>
-    <row r="14" spans="1:31">
-      <c r="A14" t="s">
-        <v>28</v>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>MSN2</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -8501,13 +7270,10 @@
       <c r="AB14">
         <v>0</v>
       </c>
-      <c r="AC14" s="3"/>
-      <c r="AD14" s="3"/>
-      <c r="AE14" s="3"/>
-    </row>
-    <row r="15" spans="1:31">
-      <c r="A15" t="s">
-        <v>30</v>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>MSN4</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -8590,13 +7356,10 @@
       <c r="AB15">
         <v>0</v>
       </c>
-      <c r="AC15" s="3"/>
-      <c r="AD15" s="3"/>
-      <c r="AE15" s="3"/>
-    </row>
-    <row r="16" spans="1:31">
-      <c r="A16" t="s">
-        <v>32</v>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>PDR1</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -8679,13 +7442,10 @@
       <c r="AB16">
         <v>0</v>
       </c>
-      <c r="AC16" s="3"/>
-      <c r="AD16" s="3"/>
-      <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="1:31">
-      <c r="A17" t="s">
-        <v>34</v>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>POP2</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -8768,13 +7528,10 @@
       <c r="AB17">
         <v>0</v>
       </c>
-      <c r="AC17" s="3"/>
-      <c r="AD17" s="3"/>
-      <c r="AE17" s="3"/>
-    </row>
-    <row r="18" spans="1:31">
-      <c r="A18" t="s">
-        <v>36</v>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>RIF1</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -8857,13 +7614,10 @@
       <c r="AB18">
         <v>0</v>
       </c>
-      <c r="AC18" s="3"/>
-      <c r="AD18" s="3"/>
-      <c r="AE18" s="3"/>
-    </row>
-    <row r="19" spans="1:31">
-      <c r="A19" t="s">
-        <v>38</v>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>RLM1</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -8946,13 +7700,10 @@
       <c r="AB19">
         <v>0</v>
       </c>
-      <c r="AC19" s="3"/>
-      <c r="AD19" s="3"/>
-      <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="1:31">
-      <c r="A20" t="s">
-        <v>40</v>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SFP1</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -9035,13 +7786,10 @@
       <c r="AB20">
         <v>0</v>
       </c>
-      <c r="AC20" s="3"/>
-      <c r="AD20" s="3"/>
-      <c r="AE20" s="3"/>
-    </row>
-    <row r="21" spans="1:31">
-      <c r="A21" t="s">
-        <v>42</v>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SNF2</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -9124,13 +7872,10 @@
       <c r="AB21">
         <v>0</v>
       </c>
-      <c r="AC21" s="3"/>
-      <c r="AD21" s="3"/>
-      <c r="AE21" s="3"/>
-    </row>
-    <row r="22" spans="1:31">
-      <c r="A22" t="s">
-        <v>44</v>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SNF6</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -9213,13 +7958,10 @@
       <c r="AB22">
         <v>0</v>
       </c>
-      <c r="AC22" s="3"/>
-      <c r="AD22" s="3"/>
-      <c r="AE22" s="3"/>
-    </row>
-    <row r="23" spans="1:31">
-      <c r="A23" t="s">
-        <v>46</v>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>STB5</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -9302,13 +8044,10 @@
       <c r="AB23">
         <v>0</v>
       </c>
-      <c r="AC23" s="3"/>
-      <c r="AD23" s="3"/>
-      <c r="AE23" s="3"/>
-    </row>
-    <row r="24" spans="1:31">
-      <c r="A24" t="s">
-        <v>48</v>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SWI5</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -9391,13 +8130,10 @@
       <c r="AB24">
         <v>0</v>
       </c>
-      <c r="AC24" s="3"/>
-      <c r="AD24" s="3"/>
-      <c r="AE24" s="3"/>
-    </row>
-    <row r="25" spans="1:31">
-      <c r="A25" t="s">
-        <v>50</v>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>YHP1</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -9480,13 +8216,10 @@
       <c r="AB25">
         <v>0</v>
       </c>
-      <c r="AC25" s="3"/>
-      <c r="AD25" s="3"/>
-      <c r="AE25" s="3"/>
-    </row>
-    <row r="26" spans="1:31">
-      <c r="A26" t="s">
-        <v>51</v>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>YLR278C</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -9569,13 +8302,10 @@
       <c r="AB26">
         <v>0</v>
       </c>
-      <c r="AC26" s="3"/>
-      <c r="AD26" s="3"/>
-      <c r="AE26" s="3"/>
-    </row>
-    <row r="27" spans="1:31">
-      <c r="A27" t="s">
-        <v>53</v>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>YOX1</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -9658,13 +8388,10 @@
       <c r="AB27">
         <v>0</v>
       </c>
-      <c r="AC27" s="3"/>
-      <c r="AD27" s="3"/>
-      <c r="AE27" s="3"/>
-    </row>
-    <row r="28" spans="1:31">
-      <c r="A28" t="s">
-        <v>55</v>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>ZAP1</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -9747,140 +8474,130 @@
       <c r="AB28">
         <v>0</v>
       </c>
-      <c r="AC28" s="3"/>
-      <c r="AD28" s="3"/>
-      <c r="AE28" s="3"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE28"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr enableFormatConditionsCalculation="0">
-    <tabColor rgb="FFFFFFFF"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="13" x14ac:dyDescent="0"/>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1E-10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>61</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>optimization_parameter</v>
+      </c>
+      <c r="B1" t="str">
+        <v>value</v>
+      </c>
+      <c r="C1" t="str">
+        <v>value</v>
+      </c>
+      <c r="D1" t="str">
+        <v>value</v>
+      </c>
+      <c r="E1" t="str">
+        <v>value</v>
+      </c>
+      <c r="F1" t="str">
+        <v>value</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>alpha</v>
+      </c>
+      <c r="B2">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>kk_max</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" s="4">
+    <row r="4">
+      <c r="A4" t="str">
+        <v>MaxIter</v>
+      </c>
+      <c r="B4">
         <v>100000000</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1E-10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="4">
+    <row r="5">
+      <c r="A5" t="str">
+        <v>TolFun</v>
+      </c>
+      <c r="B5">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>MaxFunEval</v>
+      </c>
+      <c r="B6">
         <v>100000000</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="4">
-        <v>1E-10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>66</v>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>TolX</v>
+      </c>
+      <c r="B7">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Sigmoid</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>69</v>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>iestimate</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>igraph</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>fix_P</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A12" t="s">
-        <v>70</v>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>fix_b</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A13" t="s">
-        <v>71</v>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>time</v>
       </c>
       <c r="B13">
         <v>15</v>
@@ -9892,42 +8609,42 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="5">
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Strain</v>
+      </c>
+      <c r="B14" t="str">
+        <v>wt</v>
+      </c>
+      <c r="C14" t="str">
+        <v>dcin5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Sheet</v>
+      </c>
+      <c r="B15">
         <v>3</v>
       </c>
       <c r="C15">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="5">
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Deletion</v>
+      </c>
+      <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>77</v>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>simtime</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -9970,255 +8687,245 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:N17"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr enableFormatConditionsCalculation="0">
-    <tabColor rgb="FFFFFFFF"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="13" x14ac:dyDescent="0"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>rows genes affected/cols genes controlling</v>
+      </c>
+      <c r="B1" t="str">
+        <v>threshold</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ACE2</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ASG1</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CBF1</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>CIN5</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CYC8</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>FKH2</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="2" t="s">
-        <v>16</v>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>GAT3</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="2" t="s">
-        <v>18</v>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>GCR2</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="2" t="s">
-        <v>20</v>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>GLN3</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="2" t="s">
-        <v>22</v>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>HMO1</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="2" t="s">
-        <v>24</v>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>MCM1</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="2" t="s">
-        <v>26</v>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>MIG2</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="2" t="s">
-        <v>28</v>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>MSN2</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="2" t="s">
-        <v>30</v>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>MSN4</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="2" t="s">
-        <v>32</v>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>PDR1</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="2" t="s">
-        <v>34</v>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>POP2</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="2" t="s">
-        <v>36</v>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>RIF1</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="2" t="s">
-        <v>38</v>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>RLM1</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="2" t="s">
-        <v>40</v>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SFP1</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="2" t="s">
-        <v>42</v>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SNF2</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="2" t="s">
-        <v>44</v>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SNF6</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="2" t="s">
-        <v>46</v>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>STB5</v>
       </c>
       <c r="B23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="2" t="s">
-        <v>48</v>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SWI5</v>
       </c>
       <c r="B24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="2" t="s">
-        <v>50</v>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>YHP1</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="2" t="s">
-        <v>51</v>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>YLR278C</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="2" t="s">
-        <v>53</v>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>YOX1</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="2" t="s">
-        <v>55</v>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>ZAP1</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B28"/>
+  </ignoredErrors>
 </worksheet>
 </file>